--- a/Input/student_grades_2028-2029.xlsx
+++ b/Input/student_grades_2028-2029.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suprl\OneDrive\Escritorio\MiM DSAI\S1\Python &amp; SQL Bootcamp\Multi-Track-Data-Report\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E522C2-4034-420A-818E-96AFF3DE5247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2A40F0-D9B8-476A-A9F4-293341F878C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="810" windowWidth="24150" windowHeight="13095" xr2:uid="{AF2C29EA-29F2-4E4E-92DE-18AA6D6024DD}"/>
+    <workbookView xWindow="1380" yWindow="2190" windowWidth="24150" windowHeight="13095" activeTab="1" xr2:uid="{AF2C29EA-29F2-4E4E-92DE-18AA6D6024DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Finance" sheetId="2" r:id="rId2"/>
-    <sheet name="BM" sheetId="3" r:id="rId3"/>
+    <sheet name="BM" sheetId="2" r:id="rId2"/>
+    <sheet name="Finance" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">BM!$A$1:$N$201</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$N$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Finance!$A$1:$N$201</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6553" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6517" uniqueCount="721">
   <si>
     <t>StudentID</t>
   </si>
@@ -1667,9 +1667,6 @@
     <t>76.9</t>
   </si>
   <si>
-    <t>56.1</t>
-  </si>
-  <si>
     <t>79.6</t>
   </si>
   <si>
@@ -1736,9 +1733,6 @@
     <t>53.1</t>
   </si>
   <si>
-    <t>51.6</t>
-  </si>
-  <si>
     <t>71.1</t>
   </si>
   <si>
@@ -1787,9 +1781,6 @@
     <t>95.6</t>
   </si>
   <si>
-    <t>51.1</t>
-  </si>
-  <si>
     <t>62.9</t>
   </si>
   <si>
@@ -1832,9 +1823,6 @@
     <t>94.7</t>
   </si>
   <si>
-    <t>34.3</t>
-  </si>
-  <si>
     <t>64.6</t>
   </si>
   <si>
@@ -1886,18 +1874,12 @@
     <t>78.3</t>
   </si>
   <si>
-    <t>51.4</t>
-  </si>
-  <si>
     <t>99.3</t>
   </si>
   <si>
     <t>59.9</t>
   </si>
   <si>
-    <t>54.8</t>
-  </si>
-  <si>
     <t>55.7</t>
   </si>
   <si>
@@ -1907,9 +1889,6 @@
     <t>51.8</t>
   </si>
   <si>
-    <t>70.7</t>
-  </si>
-  <si>
     <t>79.5</t>
   </si>
   <si>
@@ -1919,12 +1898,6 @@
     <t>81.4</t>
   </si>
   <si>
-    <t>35.6</t>
-  </si>
-  <si>
-    <t>40.3</t>
-  </si>
-  <si>
     <t>57.2</t>
   </si>
   <si>
@@ -1949,15 +1922,9 @@
     <t>61.1</t>
   </si>
   <si>
-    <t>94.4</t>
-  </si>
-  <si>
     <t>99.7</t>
   </si>
   <si>
-    <t>35.3</t>
-  </si>
-  <si>
     <t>88.5</t>
   </si>
   <si>
@@ -1970,9 +1937,6 @@
     <t>38.5</t>
   </si>
   <si>
-    <t>30.7</t>
-  </si>
-  <si>
     <t>38.9</t>
   </si>
   <si>
@@ -1994,9 +1958,6 @@
     <t>86.3</t>
   </si>
   <si>
-    <t>74.7</t>
-  </si>
-  <si>
     <t>97.6</t>
   </si>
   <si>
@@ -2030,12 +1991,6 @@
     <t>44.6</t>
   </si>
   <si>
-    <t>42.9</t>
-  </si>
-  <si>
-    <t>57.5</t>
-  </si>
-  <si>
     <t>58.5</t>
   </si>
   <si>
@@ -2072,9 +2027,6 @@
     <t>95.2</t>
   </si>
   <si>
-    <t>55.3</t>
-  </si>
-  <si>
     <t>50.7</t>
   </si>
   <si>
@@ -2087,9 +2039,6 @@
     <t>46.3</t>
   </si>
   <si>
-    <t>47.2</t>
-  </si>
-  <si>
     <t>56.4</t>
   </si>
   <si>
@@ -2108,9 +2057,6 @@
     <t>98.6</t>
   </si>
   <si>
-    <t>42.5</t>
-  </si>
-  <si>
     <t>96.5</t>
   </si>
   <si>
@@ -2186,9 +2132,6 @@
     <t>49.1</t>
   </si>
   <si>
-    <t>37.4</t>
-  </si>
-  <si>
     <t>32.5</t>
   </si>
   <si>
@@ -2211,9 +2154,6 @@
   </si>
   <si>
     <t>36.2</t>
-  </si>
-  <si>
-    <t>63.6</t>
   </si>
   <si>
     <t>56.7</t>
@@ -3367,8 +3307,8 @@
       <c r="F6">
         <v>100</v>
       </c>
-      <c r="G6" t="s">
-        <v>128</v>
+      <c r="G6">
+        <v>80</v>
       </c>
       <c r="H6" t="s">
         <v>50</v>
@@ -3496,11 +3436,11 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" t="s">
-        <v>67</v>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
       </c>
       <c r="H9" t="s">
         <v>68</v>
@@ -3579,13 +3519,13 @@
         <v>234</v>
       </c>
       <c r="D11" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="G11" t="s">
         <v>93</v>
@@ -3597,7 +3537,7 @@
         <v>77</v>
       </c>
       <c r="J11" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="K11" t="s">
         <v>78</v>
@@ -3685,7 +3625,7 @@
         <v>78</v>
       </c>
       <c r="J13" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="K13" t="s">
         <v>140</v>
@@ -3851,8 +3791,8 @@
       <c r="F17" t="s">
         <v>49</v>
       </c>
-      <c r="G17" t="s">
-        <v>132</v>
+      <c r="G17">
+        <v>80</v>
       </c>
       <c r="H17" t="s">
         <v>104</v>
@@ -3939,8 +3879,8 @@
       <c r="F19">
         <v>100</v>
       </c>
-      <c r="G19" t="s">
-        <v>27</v>
+      <c r="G19">
+        <v>80</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
@@ -3983,14 +3923,14 @@
       <c r="F20" t="s">
         <v>27</v>
       </c>
-      <c r="G20" t="s">
-        <v>56</v>
+      <c r="G20">
+        <v>80</v>
       </c>
       <c r="H20" t="s">
         <v>102</v>
       </c>
       <c r="I20" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="J20" t="s">
         <v>119</v>
@@ -4068,8 +4008,8 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22" t="s">
-        <v>157</v>
+      <c r="F22">
+        <v>80</v>
       </c>
       <c r="G22" t="s">
         <v>17</v>
@@ -4159,8 +4099,8 @@
       <c r="F24" t="s">
         <v>64</v>
       </c>
-      <c r="G24" t="s">
-        <v>64</v>
+      <c r="G24">
+        <v>80</v>
       </c>
       <c r="H24" t="s">
         <v>78</v>
@@ -4172,7 +4112,7 @@
         <v>100</v>
       </c>
       <c r="K24" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="L24" t="s">
         <v>61</v>
@@ -4257,7 +4197,7 @@
         <v>66</v>
       </c>
       <c r="J26" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="K26" t="s">
         <v>17</v>
@@ -4304,7 +4244,7 @@
         <v>221</v>
       </c>
       <c r="K27" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="L27" t="s">
         <v>22</v>
@@ -4339,7 +4279,7 @@
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="I28" t="s">
         <v>44</v>
@@ -4456,7 +4396,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -4464,8 +4404,8 @@
       <c r="F31" t="s">
         <v>104</v>
       </c>
-      <c r="G31" t="s">
-        <v>56</v>
+      <c r="G31">
+        <v>80</v>
       </c>
       <c r="H31" t="s">
         <v>47</v>
@@ -4521,7 +4461,7 @@
         <v>50</v>
       </c>
       <c r="K32" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -4640,8 +4580,8 @@
       <c r="F35" t="s">
         <v>26</v>
       </c>
-      <c r="G35" t="s">
-        <v>79</v>
+      <c r="G35">
+        <v>80</v>
       </c>
       <c r="H35" t="s">
         <v>66</v>
@@ -4697,7 +4637,7 @@
         <v>189</v>
       </c>
       <c r="K36" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="L36" t="s">
         <v>61</v>
@@ -4904,8 +4844,8 @@
       <c r="F41">
         <v>100</v>
       </c>
-      <c r="G41" t="s">
-        <v>130</v>
+      <c r="G41">
+        <v>80</v>
       </c>
       <c r="H41" t="s">
         <v>83</v>
@@ -4917,7 +4857,7 @@
         <v>182</v>
       </c>
       <c r="K41" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
@@ -5093,7 +5033,7 @@
         <v>153</v>
       </c>
       <c r="K45" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L45" t="s">
         <v>22</v>
@@ -5175,7 +5115,7 @@
         <v>41</v>
       </c>
       <c r="I47" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J47" t="s">
         <v>93</v>
@@ -5216,7 +5156,7 @@
         <v>99</v>
       </c>
       <c r="H48" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="I48" t="s">
         <v>31</v>
@@ -5256,8 +5196,8 @@
       <c r="F49" t="s">
         <v>31</v>
       </c>
-      <c r="G49" t="s">
-        <v>113</v>
+      <c r="G49">
+        <v>80</v>
       </c>
       <c r="H49" t="s">
         <v>93</v>
@@ -5269,7 +5209,7 @@
         <v>43</v>
       </c>
       <c r="K49" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="L49" t="s">
         <v>61</v>
@@ -5432,14 +5372,14 @@
       <c r="F53">
         <v>100</v>
       </c>
-      <c r="G53" t="s">
-        <v>157</v>
+      <c r="G53">
+        <v>80</v>
       </c>
       <c r="H53" t="s">
         <v>28</v>
       </c>
       <c r="I53" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="J53" t="s">
         <v>180</v>
@@ -5483,7 +5423,7 @@
         <v>77</v>
       </c>
       <c r="I54" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="J54" t="s">
         <v>193</v>
@@ -5703,7 +5643,7 @@
         <v>158</v>
       </c>
       <c r="I59" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="J59" t="s">
         <v>140</v>
@@ -5747,13 +5687,13 @@
         <v>44</v>
       </c>
       <c r="I60" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="J60" t="s">
         <v>82</v>
       </c>
       <c r="K60" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L60" t="s">
         <v>61</v>
@@ -5835,13 +5775,13 @@
         <v>41</v>
       </c>
       <c r="I62" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="J62" t="s">
         <v>131</v>
       </c>
       <c r="K62" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="L62" t="s">
         <v>61</v>
@@ -6181,7 +6121,7 @@
         <v>100</v>
       </c>
       <c r="G70" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="H70" t="s">
         <v>75</v>
@@ -6413,7 +6353,7 @@
         <v>118</v>
       </c>
       <c r="K75" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="L75" t="s">
         <v>61</v>
@@ -6532,8 +6472,8 @@
       <c r="F78" t="s">
         <v>78</v>
       </c>
-      <c r="G78" t="s">
-        <v>91</v>
+      <c r="G78">
+        <v>80</v>
       </c>
       <c r="H78" t="s">
         <v>58</v>
@@ -6545,7 +6485,7 @@
         <v>207</v>
       </c>
       <c r="K78" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="L78" t="s">
         <v>61</v>
@@ -6664,8 +6604,8 @@
       <c r="F81" t="s">
         <v>87</v>
       </c>
-      <c r="G81" t="s">
-        <v>92</v>
+      <c r="G81">
+        <v>25</v>
       </c>
       <c r="H81" t="s">
         <v>40</v>
@@ -6676,8 +6616,8 @@
       <c r="J81" t="s">
         <v>161</v>
       </c>
-      <c r="K81" t="s">
-        <v>40</v>
+      <c r="K81">
+        <v>25</v>
       </c>
       <c r="L81" t="s">
         <v>22</v>
@@ -6708,8 +6648,8 @@
       <c r="F82" t="s">
         <v>21</v>
       </c>
-      <c r="G82" t="s">
-        <v>67</v>
+      <c r="G82">
+        <v>80</v>
       </c>
       <c r="H82" t="s">
         <v>86</v>
@@ -6765,7 +6705,7 @@
         <v>215</v>
       </c>
       <c r="K83" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L83" t="s">
         <v>22</v>
@@ -6979,7 +6919,7 @@
         <v>48</v>
       </c>
       <c r="I88" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="J88" t="s">
         <v>217</v>
@@ -7117,7 +7057,7 @@
         <v>163</v>
       </c>
       <c r="K91" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="L91" t="s">
         <v>22</v>
@@ -7148,8 +7088,8 @@
       <c r="F92" t="s">
         <v>48</v>
       </c>
-      <c r="G92" t="s">
-        <v>126</v>
+      <c r="G92">
+        <v>80</v>
       </c>
       <c r="H92" t="s">
         <v>76</v>
@@ -7551,7 +7491,7 @@
         <v>122</v>
       </c>
       <c r="I101" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="J101" t="s">
         <v>124</v>
@@ -7838,7 +7778,7 @@
         <v>227</v>
       </c>
       <c r="C108" t="s">
-        <v>738</v>
+        <v>718</v>
       </c>
       <c r="D108" t="s">
         <v>15</v>
@@ -7994,7 +7934,7 @@
         <v>104</v>
       </c>
       <c r="K111" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="L111" t="s">
         <v>22</v>
@@ -8554,7 +8494,7 @@
         <v>40</v>
       </c>
       <c r="G124" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="H124" t="s">
         <v>52</v>
@@ -8874,7 +8814,7 @@
         <v>119</v>
       </c>
       <c r="K131" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L131" t="s">
         <v>22</v>
@@ -9126,7 +9066,7 @@
         <v>93</v>
       </c>
       <c r="G137" t="s">
-        <v>92</v>
+        <v>293</v>
       </c>
       <c r="H137" t="s">
         <v>98</v>
@@ -9170,7 +9110,7 @@
         <v>67</v>
       </c>
       <c r="G138" t="s">
-        <v>68</v>
+        <v>295</v>
       </c>
       <c r="H138" t="s">
         <v>28</v>
@@ -9214,7 +9154,7 @@
         <v>44</v>
       </c>
       <c r="G139" t="s">
-        <v>42</v>
+        <v>299</v>
       </c>
       <c r="H139" t="s">
         <v>66</v>
@@ -9258,7 +9198,7 @@
         <v>66</v>
       </c>
       <c r="G140" t="s">
-        <v>68</v>
+        <v>302</v>
       </c>
       <c r="H140" t="s">
         <v>34</v>
@@ -9302,7 +9242,7 @@
         <v>44</v>
       </c>
       <c r="G141" t="s">
-        <v>63</v>
+        <v>308</v>
       </c>
       <c r="H141" t="s">
         <v>64</v>
@@ -9343,10 +9283,10 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="G142" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
@@ -9390,7 +9330,7 @@
         <v>42</v>
       </c>
       <c r="G143" t="s">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="H143" t="s">
         <v>42</v>
@@ -9434,7 +9374,7 @@
         <v>83</v>
       </c>
       <c r="G144" t="s">
-        <v>92</v>
+        <v>320</v>
       </c>
       <c r="H144" t="s">
         <v>87</v>
@@ -9478,7 +9418,7 @@
         <v>40</v>
       </c>
       <c r="G145" t="s">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c r="H145">
         <v>100</v>
@@ -9522,7 +9462,7 @@
         <v>100</v>
       </c>
       <c r="G146" t="s">
-        <v>56</v>
+        <v>331</v>
       </c>
       <c r="H146" t="s">
         <v>30</v>
@@ -9566,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="G147" t="s">
-        <v>44</v>
+        <v>334</v>
       </c>
       <c r="H147" t="s">
         <v>93</v>
@@ -9610,7 +9550,7 @@
         <v>87</v>
       </c>
       <c r="G148" t="s">
-        <v>41</v>
+        <v>340</v>
       </c>
       <c r="H148" t="s">
         <v>26</v>
@@ -9654,7 +9594,7 @@
         <v>113</v>
       </c>
       <c r="G149" t="s">
-        <v>40</v>
+        <v>342</v>
       </c>
       <c r="H149" t="s">
         <v>114</v>
@@ -9698,7 +9638,7 @@
         <v>18</v>
       </c>
       <c r="G150" t="s">
-        <v>41</v>
+        <v>345</v>
       </c>
       <c r="H150" t="s">
         <v>113</v>
@@ -9742,7 +9682,7 @@
         <v>27</v>
       </c>
       <c r="G151" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H151" t="s">
         <v>47</v>
@@ -9785,8 +9725,8 @@
       <c r="F152" t="s">
         <v>68</v>
       </c>
-      <c r="G152">
-        <v>100</v>
+      <c r="G152" t="s">
+        <v>348</v>
       </c>
       <c r="H152" t="s">
         <v>49</v>
@@ -9830,7 +9770,7 @@
         <v>34</v>
       </c>
       <c r="G153" t="s">
-        <v>91</v>
+        <v>352</v>
       </c>
       <c r="H153" t="s">
         <v>66</v>
@@ -9874,7 +9814,7 @@
         <v>104</v>
       </c>
       <c r="G154" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="H154" t="s">
         <v>26</v>
@@ -9918,7 +9858,7 @@
         <v>38</v>
       </c>
       <c r="G155" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="H155" t="s">
         <v>87</v>
@@ -9962,7 +9902,7 @@
         <v>87</v>
       </c>
       <c r="G156" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H156" t="s">
         <v>27</v>
@@ -10006,7 +9946,7 @@
         <v>64</v>
       </c>
       <c r="G157" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="H157" t="s">
         <v>17</v>
@@ -10050,7 +9990,7 @@
         <v>66</v>
       </c>
       <c r="G158" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="H158" t="s">
         <v>31</v>
@@ -10094,7 +10034,7 @@
         <v>21</v>
       </c>
       <c r="G159" t="s">
-        <v>92</v>
+        <v>370</v>
       </c>
       <c r="H159" t="s">
         <v>93</v>
@@ -10138,7 +10078,7 @@
         <v>50</v>
       </c>
       <c r="G160" t="s">
-        <v>68</v>
+        <v>373</v>
       </c>
       <c r="H160" t="s">
         <v>33</v>
@@ -10182,7 +10122,7 @@
         <v>48</v>
       </c>
       <c r="G161" t="s">
-        <v>102</v>
+        <v>375</v>
       </c>
       <c r="H161" t="s">
         <v>69</v>
@@ -10226,7 +10166,7 @@
         <v>58</v>
       </c>
       <c r="G162" t="s">
-        <v>52</v>
+        <v>378</v>
       </c>
       <c r="H162" t="s">
         <v>92</v>
@@ -10238,7 +10178,7 @@
         <v>28</v>
       </c>
       <c r="K162" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="L162" t="s">
         <v>22</v>
@@ -10270,7 +10210,7 @@
         <v>34</v>
       </c>
       <c r="G163" t="s">
-        <v>91</v>
+        <v>381</v>
       </c>
       <c r="H163" t="s">
         <v>98</v>
@@ -10282,10 +10222,10 @@
         <v>34</v>
       </c>
       <c r="K163" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="L163" t="s">
-        <v>737</v>
+        <v>717</v>
       </c>
       <c r="M163" t="b">
         <v>0</v>
@@ -10314,7 +10254,7 @@
         <v>100</v>
       </c>
       <c r="G164" t="s">
-        <v>38</v>
+        <v>385</v>
       </c>
       <c r="H164" t="s">
         <v>93</v>
@@ -10358,7 +10298,7 @@
         <v>25</v>
       </c>
       <c r="G165" t="s">
-        <v>26</v>
+        <v>389</v>
       </c>
       <c r="H165" t="s">
         <v>27</v>
@@ -10402,7 +10342,7 @@
         <v>56</v>
       </c>
       <c r="G166" t="s">
-        <v>104</v>
+        <v>268</v>
       </c>
       <c r="H166" t="s">
         <v>44</v>
@@ -10446,7 +10386,7 @@
         <v>68</v>
       </c>
       <c r="G167" t="s">
-        <v>28</v>
+        <v>271</v>
       </c>
       <c r="H167" t="s">
         <v>74</v>
@@ -10486,11 +10426,11 @@
       <c r="E168">
         <v>2</v>
       </c>
-      <c r="F168" t="s">
-        <v>79</v>
+      <c r="F168">
+        <v>80</v>
       </c>
       <c r="G168" t="s">
-        <v>30</v>
+        <v>397</v>
       </c>
       <c r="H168" t="s">
         <v>68</v>
@@ -10534,7 +10474,7 @@
         <v>17</v>
       </c>
       <c r="G169" t="s">
-        <v>33</v>
+        <v>403</v>
       </c>
       <c r="H169" t="s">
         <v>66</v>
@@ -10578,7 +10518,7 @@
         <v>36</v>
       </c>
       <c r="G170" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="H170" t="s">
         <v>69</v>
@@ -10622,7 +10562,7 @@
         <v>21</v>
       </c>
       <c r="G171" t="s">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="H171" t="s">
         <v>104</v>
@@ -10666,7 +10606,7 @@
         <v>27</v>
       </c>
       <c r="G172" t="s">
-        <v>67</v>
+        <v>413</v>
       </c>
       <c r="H172" t="s">
         <v>66</v>
@@ -10710,7 +10650,7 @@
         <v>83</v>
       </c>
       <c r="G173" t="s">
-        <v>77</v>
+        <v>418</v>
       </c>
       <c r="H173" t="s">
         <v>52</v>
@@ -10722,7 +10662,7 @@
         <v>166</v>
       </c>
       <c r="K173" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L173" t="s">
         <v>22</v>
@@ -10754,7 +10694,7 @@
         <v>42</v>
       </c>
       <c r="G174" t="s">
-        <v>48</v>
+        <v>716</v>
       </c>
       <c r="H174" t="s">
         <v>16</v>
@@ -10766,7 +10706,7 @@
         <v>184</v>
       </c>
       <c r="K174" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="L174" t="s">
         <v>22</v>
@@ -10798,7 +10738,7 @@
         <v>44</v>
       </c>
       <c r="G175" t="s">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="H175">
         <v>100</v>
@@ -10810,7 +10750,7 @@
         <v>209</v>
       </c>
       <c r="K175" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="L175" t="s">
         <v>22</v>
@@ -10842,7 +10782,7 @@
         <v>58</v>
       </c>
       <c r="G176" t="s">
-        <v>64</v>
+        <v>426</v>
       </c>
       <c r="H176" t="s">
         <v>102</v>
@@ -10882,11 +10822,11 @@
       <c r="E177">
         <v>2</v>
       </c>
-      <c r="F177" t="s">
-        <v>157</v>
+      <c r="F177">
+        <v>80</v>
       </c>
       <c r="G177" t="s">
-        <v>33</v>
+        <v>206</v>
       </c>
       <c r="H177" t="s">
         <v>50</v>
@@ -10897,8 +10837,8 @@
       <c r="J177" t="s">
         <v>28</v>
       </c>
-      <c r="K177" t="s">
-        <v>30</v>
+      <c r="K177">
+        <v>15</v>
       </c>
       <c r="L177" t="s">
         <v>22</v>
@@ -10930,7 +10870,7 @@
         <v>76</v>
       </c>
       <c r="G178" t="s">
-        <v>19</v>
+        <v>431</v>
       </c>
       <c r="H178" t="s">
         <v>35</v>
@@ -10974,10 +10914,10 @@
         <v>100</v>
       </c>
       <c r="G179" t="s">
-        <v>21</v>
-      </c>
-      <c r="H179" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="H179">
+        <v>15</v>
       </c>
       <c r="I179" t="s">
         <v>48</v>
@@ -11018,7 +10958,7 @@
         <v>33</v>
       </c>
       <c r="G180" t="s">
-        <v>34</v>
+        <v>434</v>
       </c>
       <c r="H180" t="s">
         <v>28</v>
@@ -11061,8 +11001,8 @@
       <c r="F181" t="s">
         <v>69</v>
       </c>
-      <c r="G181">
-        <v>100</v>
+      <c r="G181" t="s">
+        <v>167</v>
       </c>
       <c r="H181" t="s">
         <v>96</v>
@@ -11106,7 +11046,7 @@
         <v>74</v>
       </c>
       <c r="G182" t="s">
-        <v>17</v>
+        <v>441</v>
       </c>
       <c r="H182" t="s">
         <v>76</v>
@@ -11150,7 +11090,7 @@
         <v>83</v>
       </c>
       <c r="G183" t="s">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="H183" t="s">
         <v>16</v>
@@ -11194,7 +11134,7 @@
         <v>93</v>
       </c>
       <c r="G184" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="H184" t="s">
         <v>72</v>
@@ -11234,11 +11174,11 @@
       <c r="E185">
         <v>1</v>
       </c>
-      <c r="F185" t="s">
-        <v>56</v>
+      <c r="F185">
+        <v>80</v>
       </c>
       <c r="G185" t="s">
-        <v>38</v>
+        <v>447</v>
       </c>
       <c r="H185" t="s">
         <v>87</v>
@@ -11282,7 +11222,7 @@
         <v>35</v>
       </c>
       <c r="G186" t="s">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="H186" t="s">
         <v>56</v>
@@ -11326,7 +11266,7 @@
         <v>83</v>
       </c>
       <c r="G187" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="H187">
         <v>100</v>
@@ -11370,7 +11310,7 @@
         <v>21</v>
       </c>
       <c r="G188" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="H188" t="s">
         <v>16</v>
@@ -11414,7 +11354,7 @@
         <v>38</v>
       </c>
       <c r="G189" t="s">
-        <v>140</v>
+        <v>303</v>
       </c>
       <c r="H189" t="s">
         <v>108</v>
@@ -11458,7 +11398,7 @@
         <v>100</v>
       </c>
       <c r="G190" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="H190" t="s">
         <v>26</v>
@@ -11542,8 +11482,8 @@
       <c r="E192">
         <v>1</v>
       </c>
-      <c r="F192" t="s">
-        <v>16</v>
+      <c r="F192">
+        <v>15</v>
       </c>
       <c r="G192" t="s">
         <v>104</v>
@@ -11677,8 +11617,8 @@
       <c r="F195" t="s">
         <v>47</v>
       </c>
-      <c r="G195" t="s">
-        <v>49</v>
+      <c r="G195">
+        <v>80</v>
       </c>
       <c r="H195" t="s">
         <v>17</v>
@@ -11857,7 +11797,7 @@
         <v>93</v>
       </c>
       <c r="H199" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="I199" t="s">
         <v>87</v>
@@ -12298,7 +12238,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="G8" t="s">
         <v>59</v>
@@ -12656,7 +12596,7 @@
         <v>308</v>
       </c>
       <c r="H16" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="I16" t="s">
         <v>310</v>
@@ -14102,7 +14042,7 @@
         <v>254</v>
       </c>
       <c r="G49" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="H49" t="s">
         <v>102</v>
@@ -14196,7 +14136,7 @@
         <v>315</v>
       </c>
       <c r="I51" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="J51" t="s">
         <v>214</v>
@@ -15111,7 +15051,7 @@
         <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="G72" t="s">
         <v>473</v>
@@ -15771,7 +15711,7 @@
         <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>190</v>
+        <v>523</v>
       </c>
       <c r="G87" t="s">
         <v>51</v>
@@ -15815,7 +15755,7 @@
         <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>299</v>
+        <v>681</v>
       </c>
       <c r="G88" t="s">
         <v>295</v>
@@ -15859,10 +15799,10 @@
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>503</v>
+        <v>429</v>
       </c>
       <c r="G89" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="H89" t="s">
         <v>505</v>
@@ -15900,7 +15840,7 @@
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>506</v>
+        <v>275</v>
       </c>
       <c r="G90" t="s">
         <v>507</v>
@@ -15944,7 +15884,7 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="G91" t="s">
         <v>392</v>
@@ -15988,7 +15928,7 @@
         <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>211</v>
+        <v>492</v>
       </c>
       <c r="G92" t="s">
         <v>450</v>
@@ -16032,13 +15972,13 @@
         <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>736</v>
+        <v>48</v>
       </c>
       <c r="G93" t="s">
         <v>219</v>
       </c>
       <c r="H93" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="I93" t="s">
         <v>415</v>
@@ -16076,7 +16016,7 @@
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G94" t="s">
         <v>492</v>
@@ -16120,7 +16060,7 @@
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
       <c r="G95" t="s">
         <v>519</v>
@@ -16164,7 +16104,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>149</v>
+        <v>688</v>
       </c>
       <c r="G96" t="s">
         <v>433</v>
@@ -16208,7 +16148,7 @@
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="G97" t="s">
         <v>413</v>
@@ -16252,7 +16192,7 @@
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="G98" t="s">
         <v>166</v>
@@ -16296,7 +16236,7 @@
         <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="G99" t="s">
         <v>360</v>
@@ -16340,7 +16280,7 @@
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="G100" t="s">
         <v>291</v>
@@ -16384,7 +16324,7 @@
         <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>320</v>
+        <v>503</v>
       </c>
       <c r="G101" t="s">
         <v>117</v>
@@ -16428,7 +16368,7 @@
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>478</v>
+        <v>365</v>
       </c>
       <c r="G102" t="s">
         <v>395</v>
@@ -16472,7 +16412,7 @@
         <v>2</v>
       </c>
       <c r="F103" t="s">
-        <v>194</v>
+        <v>518</v>
       </c>
       <c r="G103" t="s">
         <v>253</v>
@@ -16516,7 +16456,7 @@
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>92</v>
+        <v>492</v>
       </c>
       <c r="G104" t="s">
         <v>149</v>
@@ -16560,7 +16500,7 @@
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>162</v>
+        <v>694</v>
       </c>
       <c r="G105" t="s">
         <v>314</v>
@@ -16604,7 +16544,7 @@
         <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>332</v>
+        <v>655</v>
       </c>
       <c r="G106" t="s">
         <v>531</v>
@@ -16648,7 +16588,7 @@
         <v>2</v>
       </c>
       <c r="F107" t="s">
-        <v>533</v>
+        <v>397</v>
       </c>
       <c r="G107" t="s">
         <v>289</v>
@@ -16692,7 +16632,7 @@
         <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>295</v>
+        <v>172</v>
       </c>
       <c r="G108" t="s">
         <v>368</v>
@@ -16736,7 +16676,7 @@
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>536</v>
+        <v>444</v>
       </c>
       <c r="G109" t="s">
         <v>143</v>
@@ -16780,7 +16720,7 @@
         <v>2</v>
       </c>
       <c r="F110" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="G110" t="s">
         <v>507</v>
@@ -16824,7 +16764,7 @@
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>540</v>
+        <v>199</v>
       </c>
       <c r="G111" t="s">
         <v>450</v>
@@ -16868,7 +16808,7 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="G112" t="s">
         <v>373</v>
@@ -16912,16 +16852,16 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="G113" t="s">
         <v>297</v>
       </c>
       <c r="H113" t="s">
+        <v>542</v>
+      </c>
+      <c r="I113" t="s">
         <v>543</v>
-      </c>
-      <c r="I113" t="s">
-        <v>544</v>
       </c>
       <c r="J113" t="s">
         <v>250</v>
@@ -16956,22 +16896,22 @@
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="G114" t="s">
         <v>249</v>
       </c>
       <c r="H114" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="I114" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J114" t="s">
         <v>170</v>
       </c>
       <c r="K114" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L114" t="s">
         <v>22</v>
@@ -17000,13 +16940,13 @@
         <v>2</v>
       </c>
       <c r="F115" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="G115" t="s">
         <v>256</v>
       </c>
       <c r="H115" t="s">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="I115" t="s">
         <v>298</v>
@@ -17044,13 +16984,13 @@
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>201</v>
+        <v>72</v>
       </c>
       <c r="G116" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H116" t="s">
-        <v>390</v>
+        <v>31</v>
       </c>
       <c r="I116" t="s">
         <v>158</v>
@@ -17059,7 +16999,7 @@
         <v>462</v>
       </c>
       <c r="K116" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L116" t="s">
         <v>22</v>
@@ -17088,13 +17028,13 @@
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>520</v>
+        <v>416</v>
       </c>
       <c r="G117" t="s">
         <v>209</v>
       </c>
       <c r="H117" t="s">
-        <v>516</v>
+        <v>326</v>
       </c>
       <c r="I117" t="s">
         <v>41</v>
@@ -17103,7 +17043,7 @@
         <v>20</v>
       </c>
       <c r="K117" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L117" t="s">
         <v>22</v>
@@ -17132,13 +17072,13 @@
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>551</v>
+        <v>696</v>
       </c>
       <c r="G118" t="s">
         <v>267</v>
       </c>
       <c r="H118" t="s">
-        <v>474</v>
+        <v>210</v>
       </c>
       <c r="I118" t="s">
         <v>30</v>
@@ -17147,7 +17087,7 @@
         <v>101</v>
       </c>
       <c r="K118" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L118" t="s">
         <v>22</v>
@@ -17176,19 +17116,19 @@
         <v>2</v>
       </c>
       <c r="F119" t="s">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="G119" t="s">
         <v>505</v>
       </c>
       <c r="H119" t="s">
-        <v>536</v>
+        <v>646</v>
       </c>
       <c r="I119" t="s">
         <v>273</v>
       </c>
       <c r="J119" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K119" t="s">
         <v>358</v>
@@ -17220,22 +17160,22 @@
         <v>1</v>
       </c>
       <c r="F120" t="s">
+        <v>356</v>
+      </c>
+      <c r="G120" t="s">
         <v>554</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
+        <v>72</v>
+      </c>
+      <c r="I120" t="s">
         <v>555</v>
-      </c>
-      <c r="H120" t="s">
-        <v>417</v>
-      </c>
-      <c r="I120" t="s">
-        <v>556</v>
       </c>
       <c r="J120" t="s">
         <v>196</v>
       </c>
       <c r="K120" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L120" t="s">
         <v>22</v>
@@ -17264,19 +17204,19 @@
         <v>2</v>
       </c>
       <c r="F121" t="s">
-        <v>137</v>
+        <v>697</v>
       </c>
       <c r="G121" t="s">
         <v>520</v>
       </c>
       <c r="H121" t="s">
-        <v>558</v>
+        <v>149</v>
       </c>
       <c r="I121" t="s">
         <v>178</v>
       </c>
       <c r="J121" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K121" t="s">
         <v>171</v>
@@ -17308,16 +17248,16 @@
         <v>2</v>
       </c>
       <c r="F122" t="s">
-        <v>559</v>
+        <v>267</v>
       </c>
       <c r="G122" t="s">
         <v>441</v>
       </c>
       <c r="H122" t="s">
-        <v>180</v>
+        <v>649</v>
       </c>
       <c r="I122" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J122" t="s">
         <v>211</v>
@@ -17352,13 +17292,13 @@
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>561</v>
+        <v>666</v>
       </c>
       <c r="G123" t="s">
         <v>103</v>
       </c>
       <c r="H123" t="s">
-        <v>562</v>
+        <v>180</v>
       </c>
       <c r="I123" t="s">
         <v>201</v>
@@ -17367,7 +17307,7 @@
         <v>518</v>
       </c>
       <c r="K123" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L123" t="s">
         <v>22</v>
@@ -17396,13 +17336,13 @@
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>564</v>
+        <v>94</v>
       </c>
       <c r="G124" t="s">
         <v>282</v>
       </c>
       <c r="H124" t="s">
-        <v>565</v>
+        <v>107</v>
       </c>
       <c r="I124" t="s">
         <v>80</v>
@@ -17440,19 +17380,19 @@
         <v>2</v>
       </c>
       <c r="F125" t="s">
-        <v>195</v>
+        <v>522</v>
       </c>
       <c r="G125" t="s">
         <v>381</v>
       </c>
       <c r="H125" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="I125" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J125" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="K125" t="s">
         <v>482</v>
@@ -17484,22 +17424,22 @@
         <v>2</v>
       </c>
       <c r="F126" t="s">
-        <v>568</v>
+        <v>446</v>
       </c>
       <c r="G126" t="s">
         <v>313</v>
       </c>
       <c r="H126" t="s">
-        <v>56</v>
+        <v>458</v>
       </c>
       <c r="I126" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J126" t="s">
         <v>328</v>
       </c>
       <c r="K126" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="L126" t="s">
         <v>22</v>
@@ -17528,13 +17468,13 @@
         <v>1</v>
       </c>
       <c r="F127" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G127" t="s">
         <v>299</v>
       </c>
       <c r="H127" t="s">
-        <v>532</v>
+        <v>27</v>
       </c>
       <c r="I127" t="s">
         <v>174</v>
@@ -17572,16 +17512,16 @@
         <v>2</v>
       </c>
       <c r="F128" t="s">
-        <v>481</v>
+        <v>699</v>
       </c>
       <c r="G128" t="s">
         <v>487</v>
       </c>
       <c r="H128" t="s">
-        <v>211</v>
+        <v>650</v>
       </c>
       <c r="I128" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J128" t="s">
         <v>26</v>
@@ -17616,13 +17556,13 @@
         <v>2</v>
       </c>
       <c r="F129" t="s">
-        <v>572</v>
+        <v>250</v>
       </c>
       <c r="G129" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H129" t="s">
-        <v>467</v>
+        <v>198</v>
       </c>
       <c r="I129" t="s">
         <v>434</v>
@@ -17631,7 +17571,7 @@
         <v>204</v>
       </c>
       <c r="K129" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="L129" t="s">
         <v>22</v>
@@ -17660,16 +17600,16 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>152</v>
+        <v>546</v>
       </c>
       <c r="G130" t="s">
         <v>33</v>
       </c>
       <c r="H130" t="s">
-        <v>54</v>
+        <v>418</v>
       </c>
       <c r="I130" t="s">
-        <v>332</v>
+        <v>72</v>
       </c>
       <c r="J130" t="s">
         <v>323</v>
@@ -17704,19 +17644,19 @@
         <v>2</v>
       </c>
       <c r="F131" t="s">
-        <v>192</v>
+        <v>434</v>
       </c>
       <c r="G131" t="s">
         <v>300</v>
       </c>
       <c r="H131" t="s">
-        <v>380</v>
+        <v>632</v>
       </c>
       <c r="I131" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="K131" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="L131" t="s">
         <v>22</v>
@@ -17745,19 +17685,19 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="G132" t="s">
         <v>167</v>
       </c>
       <c r="H132" t="s">
-        <v>104</v>
+        <v>604</v>
       </c>
       <c r="I132" t="s">
-        <v>576</v>
+        <v>18</v>
       </c>
       <c r="J132" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K132" t="s">
         <v>422</v>
@@ -17789,16 +17729,16 @@
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>352</v>
+        <v>636</v>
       </c>
       <c r="G133" t="s">
         <v>300</v>
       </c>
       <c r="H133" t="s">
-        <v>79</v>
-      </c>
-      <c r="I133" t="s">
-        <v>578</v>
+        <v>43</v>
+      </c>
+      <c r="I133">
+        <v>100</v>
       </c>
       <c r="J133" t="s">
         <v>152</v>
@@ -17833,16 +17773,16 @@
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>392</v>
+        <v>311</v>
       </c>
       <c r="G134" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H134" t="s">
-        <v>580</v>
+        <v>84</v>
       </c>
       <c r="I134" t="s">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="J134" t="s">
         <v>93</v>
@@ -17877,16 +17817,16 @@
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="G135" t="s">
         <v>98</v>
       </c>
       <c r="H135" t="s">
-        <v>581</v>
+        <v>271</v>
       </c>
       <c r="I135" t="s">
-        <v>257</v>
+        <v>68</v>
       </c>
       <c r="J135" t="s">
         <v>109</v>
@@ -17921,22 +17861,22 @@
         <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>161</v>
+        <v>496</v>
       </c>
       <c r="G136" t="s">
         <v>126</v>
       </c>
       <c r="H136" t="s">
-        <v>433</v>
+        <v>207</v>
       </c>
       <c r="I136" t="s">
-        <v>582</v>
+        <v>25</v>
       </c>
       <c r="J136" t="s">
         <v>65</v>
       </c>
       <c r="K136" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L136" t="s">
         <v>22</v>
@@ -17965,22 +17905,22 @@
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G137" t="s">
         <v>405</v>
       </c>
       <c r="H137" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="I137" t="s">
-        <v>255</v>
+        <v>35</v>
       </c>
       <c r="J137" t="s">
         <v>138</v>
       </c>
       <c r="K137" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="L137" t="s">
         <v>22</v>
@@ -18009,16 +17949,16 @@
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="G138" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="H138" t="s">
-        <v>395</v>
+        <v>56</v>
       </c>
       <c r="I138" t="s">
-        <v>518</v>
+        <v>69</v>
       </c>
       <c r="J138" t="s">
         <v>396</v>
@@ -18053,19 +17993,19 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G139" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="H139" t="s">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="I139" t="s">
-        <v>476</v>
+        <v>47</v>
       </c>
       <c r="J139" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="K139" t="s">
         <v>437</v>
@@ -18097,22 +18037,22 @@
         <v>2</v>
       </c>
       <c r="F140" t="s">
-        <v>126</v>
+        <v>271</v>
       </c>
       <c r="G140" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="H140" t="s">
-        <v>89</v>
+        <v>643</v>
       </c>
       <c r="I140" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="J140" t="s">
         <v>541</v>
       </c>
       <c r="K140" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="L140" t="s">
         <v>22</v>
@@ -18141,16 +18081,16 @@
         <v>2</v>
       </c>
       <c r="F141" t="s">
-        <v>281</v>
+        <v>590</v>
       </c>
       <c r="G141" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H141" t="s">
-        <v>404</v>
+        <v>298</v>
       </c>
       <c r="I141" t="s">
-        <v>345</v>
+        <v>27</v>
       </c>
       <c r="J141" t="s">
         <v>163</v>
@@ -18185,16 +18125,16 @@
         <v>2</v>
       </c>
       <c r="F142" t="s">
-        <v>325</v>
+        <v>702</v>
       </c>
       <c r="G142" t="s">
         <v>464</v>
       </c>
       <c r="H142" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="I142" t="s">
-        <v>358</v>
+        <v>50</v>
       </c>
       <c r="J142" t="s">
         <v>151</v>
@@ -18229,16 +18169,16 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>432</v>
+        <v>198</v>
       </c>
       <c r="G143" t="s">
         <v>368</v>
       </c>
       <c r="H143" t="s">
-        <v>291</v>
+        <v>408</v>
       </c>
       <c r="I143" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="J143" t="s">
         <v>279</v>
@@ -18273,22 +18213,22 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>138</v>
+        <v>560</v>
       </c>
       <c r="G144" t="s">
         <v>483</v>
       </c>
       <c r="H144" t="s">
-        <v>417</v>
+        <v>107</v>
       </c>
       <c r="I144" t="s">
-        <v>589</v>
+        <v>83</v>
       </c>
       <c r="J144" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="K144" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L144" t="s">
         <v>22</v>
@@ -18317,22 +18257,22 @@
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>276</v>
+        <v>581</v>
       </c>
       <c r="G145" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="H145" t="s">
-        <v>592</v>
+        <v>664</v>
       </c>
       <c r="I145" t="s">
-        <v>593</v>
+        <v>42</v>
       </c>
       <c r="J145" t="s">
         <v>412</v>
       </c>
       <c r="K145" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L145" t="s">
         <v>22</v>
@@ -18361,16 +18301,16 @@
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>595</v>
+        <v>636</v>
       </c>
       <c r="G146" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H146" t="s">
-        <v>565</v>
+        <v>659</v>
       </c>
       <c r="I146" t="s">
-        <v>312</v>
+        <v>16</v>
       </c>
       <c r="J146" t="s">
         <v>63</v>
@@ -18405,19 +18345,19 @@
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>597</v>
+        <v>714</v>
       </c>
       <c r="G147" t="s">
         <v>332</v>
       </c>
       <c r="H147" t="s">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="I147" t="s">
-        <v>534</v>
+        <v>92</v>
       </c>
       <c r="J147" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="K147" t="s">
         <v>372</v>
@@ -18449,16 +18389,16 @@
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>600</v>
+        <v>399</v>
       </c>
       <c r="G148" t="s">
         <v>535</v>
       </c>
       <c r="H148" t="s">
-        <v>54</v>
+        <v>331</v>
       </c>
       <c r="I148" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="J148" t="s">
         <v>191</v>
@@ -18493,22 +18433,22 @@
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>601</v>
+        <v>33</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
       </c>
       <c r="H149" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="I149" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J149" t="s">
         <v>68</v>
       </c>
       <c r="K149" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="L149" t="s">
         <v>22</v>
@@ -18537,19 +18477,19 @@
         <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>603</v>
+        <v>699</v>
       </c>
       <c r="G150" t="s">
         <v>164</v>
       </c>
       <c r="H150" t="s">
-        <v>537</v>
+        <v>441</v>
       </c>
       <c r="I150" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J150" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="K150" t="s">
         <v>145</v>
@@ -18581,22 +18521,22 @@
         <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>605</v>
+        <v>168</v>
       </c>
       <c r="G151" t="s">
         <v>101</v>
       </c>
       <c r="H151" t="s">
-        <v>416</v>
+        <v>646</v>
       </c>
       <c r="I151" t="s">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="J151" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="K151" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="L151" t="s">
         <v>22</v>
@@ -18625,16 +18565,16 @@
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>28</v>
+        <v>557</v>
       </c>
       <c r="G152" t="s">
         <v>34</v>
       </c>
       <c r="H152" t="s">
-        <v>52</v>
+        <v>564</v>
       </c>
       <c r="I152" t="s">
-        <v>608</v>
+        <v>42</v>
       </c>
       <c r="J152" t="s">
         <v>93</v>
@@ -18669,16 +18609,16 @@
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>609</v>
+        <v>308</v>
       </c>
       <c r="G153" t="s">
         <v>280</v>
       </c>
       <c r="H153" t="s">
-        <v>422</v>
+        <v>257</v>
       </c>
       <c r="I153" t="s">
-        <v>610</v>
+        <v>86</v>
       </c>
       <c r="J153" t="s">
         <v>32</v>
@@ -18713,16 +18653,16 @@
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>453</v>
+        <v>606</v>
       </c>
       <c r="G154" t="s">
         <v>467</v>
       </c>
       <c r="H154" t="s">
-        <v>611</v>
+        <v>667</v>
       </c>
       <c r="I154" t="s">
-        <v>253</v>
+        <v>87</v>
       </c>
       <c r="J154" t="s">
         <v>435</v>
@@ -18757,16 +18697,16 @@
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G155" t="s">
         <v>343</v>
       </c>
       <c r="H155" t="s">
-        <v>296</v>
+        <v>118</v>
       </c>
       <c r="I155" t="s">
-        <v>488</v>
+        <v>30</v>
       </c>
       <c r="J155" t="s">
         <v>69</v>
@@ -18807,10 +18747,10 @@
         <v>513</v>
       </c>
       <c r="H156" t="s">
-        <v>199</v>
+        <v>378</v>
       </c>
       <c r="I156" t="s">
-        <v>413</v>
+        <v>19</v>
       </c>
       <c r="J156" t="s">
         <v>18</v>
@@ -18851,13 +18791,13 @@
         <v>533</v>
       </c>
       <c r="H157" t="s">
-        <v>387</v>
+        <v>487</v>
       </c>
       <c r="I157" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="J157" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="K157" t="s">
         <v>124</v>
@@ -18889,16 +18829,16 @@
         <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G158" t="s">
         <v>140</v>
       </c>
       <c r="H158" t="s">
-        <v>150</v>
+        <v>463</v>
       </c>
       <c r="I158" t="s">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="J158" t="s">
         <v>82</v>
@@ -18936,16 +18876,16 @@
         <v>113</v>
       </c>
       <c r="G159" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H159" t="s">
-        <v>159</v>
+        <v>312</v>
       </c>
       <c r="I159" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="J159" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="K159" t="s">
         <v>70</v>
@@ -18983,10 +18923,10 @@
         <v>352</v>
       </c>
       <c r="H160" t="s">
-        <v>106</v>
+        <v>308</v>
       </c>
       <c r="I160" t="s">
-        <v>615</v>
+        <v>102</v>
       </c>
       <c r="J160" t="s">
         <v>296</v>
@@ -19027,13 +18967,13 @@
         <v>318</v>
       </c>
       <c r="H161" t="s">
-        <v>317</v>
+        <v>438</v>
       </c>
       <c r="I161" t="s">
-        <v>444</v>
+        <v>47</v>
       </c>
       <c r="J161" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K161" t="s">
         <v>177</v>
@@ -19068,16 +19008,16 @@
         <v>309</v>
       </c>
       <c r="G162" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H162" t="s">
-        <v>467</v>
+        <v>646</v>
       </c>
       <c r="I162" t="s">
-        <v>506</v>
+        <v>35</v>
       </c>
       <c r="J162" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="K162" t="s">
         <v>461</v>
@@ -19112,13 +19052,13 @@
         <v>108</v>
       </c>
       <c r="G163" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="H163" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="I163" t="s">
-        <v>411</v>
+        <v>158</v>
       </c>
       <c r="J163" t="s">
         <v>409</v>
@@ -19159,16 +19099,16 @@
         <v>301</v>
       </c>
       <c r="H164" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="I164" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="J164" t="s">
         <v>168</v>
       </c>
       <c r="K164" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="L164" t="s">
         <v>22</v>
@@ -19203,10 +19143,10 @@
         <v>156</v>
       </c>
       <c r="H165" t="s">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="I165" t="s">
-        <v>434</v>
+        <v>25</v>
       </c>
       <c r="J165" t="s">
         <v>100</v>
@@ -19241,16 +19181,16 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="G166" t="s">
         <v>159</v>
       </c>
       <c r="H166" t="s">
-        <v>449</v>
+        <v>615</v>
       </c>
       <c r="I166" t="s">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="J166" t="s">
         <v>84</v>
@@ -19291,10 +19231,10 @@
         <v>462</v>
       </c>
       <c r="H167" t="s">
-        <v>171</v>
+        <v>640</v>
       </c>
       <c r="I167" t="s">
-        <v>217</v>
+        <v>58</v>
       </c>
       <c r="J167" t="s">
         <v>215</v>
@@ -19335,10 +19275,10 @@
         <v>288</v>
       </c>
       <c r="H168" t="s">
-        <v>620</v>
+        <v>529</v>
       </c>
       <c r="I168" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="J168" t="s">
         <v>431</v>
@@ -19376,13 +19316,13 @@
         <v>192</v>
       </c>
       <c r="G169" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="H169" t="s">
-        <v>517</v>
+        <v>361</v>
       </c>
       <c r="I169" t="s">
-        <v>621</v>
+        <v>64</v>
       </c>
       <c r="J169" t="s">
         <v>152</v>
@@ -19423,16 +19363,16 @@
         <v>381</v>
       </c>
       <c r="H170" t="s">
-        <v>590</v>
+        <v>334</v>
       </c>
       <c r="I170" t="s">
-        <v>622</v>
+        <v>83</v>
       </c>
       <c r="J170" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="K170" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="L170" t="s">
         <v>22</v>
@@ -19464,19 +19404,19 @@
         <v>293</v>
       </c>
       <c r="G171" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H171" t="s">
-        <v>99</v>
+        <v>491</v>
       </c>
       <c r="I171" t="s">
-        <v>512</v>
+        <v>47</v>
       </c>
       <c r="J171" t="s">
         <v>384</v>
       </c>
       <c r="K171" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="L171" t="s">
         <v>22</v>
@@ -19505,7 +19445,7 @@
         <v>2</v>
       </c>
       <c r="F172" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="G172" t="s">
         <v>509</v>
@@ -19514,7 +19454,7 @@
         <v>503</v>
       </c>
       <c r="I172" t="s">
-        <v>626</v>
+        <v>27</v>
       </c>
       <c r="J172" t="s">
         <v>422</v>
@@ -19558,13 +19498,13 @@
         <v>520</v>
       </c>
       <c r="I173" t="s">
-        <v>627</v>
+        <v>64</v>
       </c>
       <c r="J173" t="s">
         <v>159</v>
       </c>
       <c r="K173" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="L173" t="s">
         <v>22</v>
@@ -19593,16 +19533,16 @@
         <v>1</v>
       </c>
       <c r="F174" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="G174" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H174" t="s">
         <v>50</v>
       </c>
       <c r="I174" t="s">
-        <v>615</v>
+        <v>68</v>
       </c>
       <c r="J174" t="s">
         <v>121</v>
@@ -19646,10 +19586,10 @@
         <v>17</v>
       </c>
       <c r="I175" t="s">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="K175" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="L175" t="s">
         <v>22</v>
@@ -19678,22 +19618,22 @@
         <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="G176" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H176" t="s">
         <v>404</v>
       </c>
       <c r="I176" t="s">
-        <v>478</v>
+        <v>87</v>
       </c>
       <c r="J176" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="K176" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="L176" t="s">
         <v>22</v>
@@ -19725,19 +19665,19 @@
         <v>192</v>
       </c>
       <c r="G177" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="H177" t="s">
         <v>338</v>
       </c>
       <c r="I177" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="J177" t="s">
         <v>188</v>
       </c>
       <c r="K177" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="L177" t="s">
         <v>22</v>
@@ -19766,7 +19706,7 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="G178" t="s">
         <v>156</v>
@@ -19775,10 +19715,10 @@
         <v>126</v>
       </c>
       <c r="I178" t="s">
-        <v>636</v>
+        <v>99</v>
       </c>
       <c r="J178" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="K178" t="s">
         <v>189</v>
@@ -19819,7 +19759,7 @@
         <v>439</v>
       </c>
       <c r="I179" t="s">
-        <v>437</v>
+        <v>48</v>
       </c>
       <c r="J179" t="s">
         <v>184</v>
@@ -19857,19 +19797,19 @@
         <v>204</v>
       </c>
       <c r="G180" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H180" t="s">
         <v>361</v>
       </c>
-      <c r="I180" t="s">
-        <v>638</v>
+      <c r="I180">
+        <v>100</v>
       </c>
       <c r="J180" t="s">
         <v>143</v>
       </c>
       <c r="K180" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="L180" t="s">
         <v>22</v>
@@ -19906,8 +19846,8 @@
       <c r="H181" t="s">
         <v>88</v>
       </c>
-      <c r="I181" t="s">
-        <v>191</v>
+      <c r="I181">
+        <v>100</v>
       </c>
       <c r="J181" t="s">
         <v>188</v>
@@ -19942,16 +19882,16 @@
         <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="G182" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H182" t="s">
         <v>357</v>
       </c>
       <c r="I182" t="s">
-        <v>640</v>
+        <v>96</v>
       </c>
       <c r="J182" t="s">
         <v>147</v>
@@ -19986,7 +19926,7 @@
         <v>2</v>
       </c>
       <c r="F183" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="G183" t="s">
         <v>405</v>
@@ -19995,7 +19935,7 @@
         <v>335</v>
       </c>
       <c r="I183" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="J183" t="s">
         <v>433</v>
@@ -20036,10 +19976,10 @@
         <v>353</v>
       </c>
       <c r="H184" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="I184" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="J184" t="s">
         <v>166</v>
@@ -20074,7 +20014,7 @@
         <v>1</v>
       </c>
       <c r="F185" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="G185" t="s">
         <v>479</v>
@@ -20083,13 +20023,13 @@
         <v>141</v>
       </c>
       <c r="I185" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="J185" t="s">
         <v>136</v>
       </c>
       <c r="K185" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="L185" t="s">
         <v>22</v>
@@ -20127,7 +20067,7 @@
         <v>69</v>
       </c>
       <c r="I186" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J186" t="s">
         <v>269</v>
@@ -20171,7 +20111,7 @@
         <v>294</v>
       </c>
       <c r="I187" t="s">
-        <v>643</v>
+        <v>47</v>
       </c>
       <c r="J187" t="s">
         <v>435</v>
@@ -20209,16 +20149,16 @@
         <v>100</v>
       </c>
       <c r="G188" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="H188" t="s">
         <v>298</v>
       </c>
       <c r="I188" t="s">
-        <v>340</v>
+        <v>17</v>
       </c>
       <c r="J188" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K188" t="s">
         <v>481</v>
@@ -20253,19 +20193,19 @@
         <v>407</v>
       </c>
       <c r="G189" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="H189" t="s">
         <v>334</v>
       </c>
-      <c r="I189" t="s">
-        <v>618</v>
+      <c r="I189">
+        <v>100</v>
       </c>
       <c r="J189" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="K189" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="L189" t="s">
         <v>22</v>
@@ -20294,7 +20234,7 @@
         <v>2</v>
       </c>
       <c r="F190" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="G190" t="s">
         <v>188</v>
@@ -20303,7 +20243,7 @@
         <v>158</v>
       </c>
       <c r="I190" t="s">
-        <v>546</v>
+        <v>44</v>
       </c>
       <c r="J190" t="s">
         <v>206</v>
@@ -20341,16 +20281,16 @@
         <v>326</v>
       </c>
       <c r="G191" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H191" t="s">
         <v>204</v>
       </c>
       <c r="I191" t="s">
-        <v>283</v>
+        <v>69</v>
       </c>
       <c r="J191" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="K191" t="s">
         <v>170</v>
@@ -20385,16 +20325,16 @@
         <v>461</v>
       </c>
       <c r="G192" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="H192" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="I192" t="s">
-        <v>326</v>
+        <v>44</v>
       </c>
       <c r="J192" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="K192" t="s">
         <v>443</v>
@@ -20429,16 +20369,16 @@
         <v>203</v>
       </c>
       <c r="G193" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="H193" t="s">
         <v>32</v>
       </c>
       <c r="I193" t="s">
-        <v>585</v>
+        <v>69</v>
       </c>
       <c r="K193" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="L193" t="s">
         <v>22</v>
@@ -20476,7 +20416,7 @@
         <v>383</v>
       </c>
       <c r="I194" t="s">
-        <v>651</v>
+        <v>28</v>
       </c>
       <c r="J194" t="s">
         <v>188</v>
@@ -20511,7 +20451,7 @@
         <v>2</v>
       </c>
       <c r="F195" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="G195" t="s">
         <v>178</v>
@@ -20520,7 +20460,7 @@
         <v>431</v>
       </c>
       <c r="I195" t="s">
-        <v>538</v>
+        <v>96</v>
       </c>
       <c r="J195" t="s">
         <v>38</v>
@@ -20558,13 +20498,13 @@
         <v>181</v>
       </c>
       <c r="G196" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="H196" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="I196" t="s">
-        <v>379</v>
+        <v>38</v>
       </c>
       <c r="J196" t="s">
         <v>186</v>
@@ -20599,7 +20539,7 @@
         <v>2</v>
       </c>
       <c r="F197" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="G197" t="s">
         <v>400</v>
@@ -20608,13 +20548,13 @@
         <v>531</v>
       </c>
       <c r="I197" t="s">
-        <v>293</v>
+        <v>98</v>
       </c>
       <c r="J197" t="s">
         <v>151</v>
       </c>
       <c r="K197" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="L197" t="s">
         <v>22</v>
@@ -20652,7 +20592,7 @@
         <v>166</v>
       </c>
       <c r="I198" t="s">
-        <v>653</v>
+        <v>28</v>
       </c>
       <c r="J198" t="s">
         <v>118</v>
@@ -20687,22 +20627,22 @@
         <v>2</v>
       </c>
       <c r="F199" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="G199" t="s">
         <v>466</v>
       </c>
       <c r="H199" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="I199" t="s">
-        <v>452</v>
+        <v>87</v>
       </c>
       <c r="J199" t="s">
         <v>357</v>
       </c>
       <c r="K199" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="L199" t="s">
         <v>61</v>
@@ -20731,7 +20671,7 @@
         <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G200" t="s">
         <v>483</v>
@@ -20740,13 +20680,13 @@
         <v>283</v>
       </c>
       <c r="I200" t="s">
-        <v>560</v>
+        <v>81</v>
       </c>
       <c r="J200" t="s">
         <v>176</v>
       </c>
       <c r="K200" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="L200" t="s">
         <v>22</v>
@@ -20775,7 +20715,7 @@
         <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="G201" t="s">
         <v>466</v>
@@ -20784,7 +20724,7 @@
         <v>311</v>
       </c>
       <c r="I201" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J201" t="s">
         <v>513</v>
@@ -20938,7 +20878,7 @@
         <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="J3" t="s">
         <v>174</v>
@@ -20973,13 +20913,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="I4" t="s">
         <v>443</v>
@@ -21032,7 +20972,7 @@
         <v>162</v>
       </c>
       <c r="K5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -21061,7 +21001,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G6" t="s">
         <v>210</v>
@@ -21070,7 +21010,7 @@
         <v>308</v>
       </c>
       <c r="I6" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="J6" t="s">
         <v>331</v>
@@ -21105,10 +21045,10 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="G7" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="H7" t="s">
         <v>43</v>
@@ -21120,10 +21060,10 @@
         <v>451</v>
       </c>
       <c r="K7" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="L7" t="s">
-        <v>735</v>
+        <v>715</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -21149,13 +21089,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="G8" t="s">
         <v>72</v>
       </c>
       <c r="H8" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="I8" t="s">
         <v>363</v>
@@ -21193,22 +21133,22 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="G9" t="s">
         <v>149</v>
       </c>
       <c r="H9" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="I9" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="J9" t="s">
         <v>301</v>
       </c>
       <c r="K9" t="s">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="L9" t="s">
         <v>22</v>
@@ -21240,7 +21180,7 @@
         <v>116</v>
       </c>
       <c r="G10" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="H10" t="s">
         <v>162</v>
@@ -21252,7 +21192,7 @@
         <v>492</v>
       </c>
       <c r="K10" t="s">
-        <v>274</v>
+        <v>450</v>
       </c>
       <c r="L10" t="s">
         <v>22</v>
@@ -21296,7 +21236,7 @@
         <v>404</v>
       </c>
       <c r="K11" t="s">
-        <v>115</v>
+        <v>291</v>
       </c>
       <c r="L11" t="s">
         <v>22</v>
@@ -21340,7 +21280,7 @@
         <v>442</v>
       </c>
       <c r="K12" t="s">
-        <v>663</v>
+        <v>413</v>
       </c>
       <c r="L12" t="s">
         <v>22</v>
@@ -21369,22 +21309,22 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="G13" t="s">
         <v>472</v>
       </c>
       <c r="H13" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I13" t="s">
         <v>356</v>
       </c>
       <c r="J13" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="K13" t="s">
-        <v>455</v>
+        <v>95</v>
       </c>
       <c r="L13" t="s">
         <v>22</v>
@@ -21413,7 +21353,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="G14" t="s">
         <v>458</v>
@@ -21428,7 +21368,7 @@
         <v>367</v>
       </c>
       <c r="K14" t="s">
-        <v>664</v>
+        <v>510</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
@@ -21466,13 +21406,13 @@
         <v>500</v>
       </c>
       <c r="I15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J15" t="s">
         <v>37</v>
       </c>
       <c r="K15" t="s">
-        <v>562</v>
+        <v>51</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
@@ -21504,19 +21444,19 @@
         <v>212</v>
       </c>
       <c r="G16" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="H16" t="s">
         <v>515</v>
       </c>
       <c r="I16" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J16" t="s">
         <v>173</v>
       </c>
       <c r="K16" t="s">
-        <v>660</v>
+        <v>514</v>
       </c>
       <c r="L16" t="s">
         <v>22</v>
@@ -21545,7 +21485,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="G17" t="s">
         <v>198</v>
@@ -21554,13 +21494,13 @@
         <v>457</v>
       </c>
       <c r="I17" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="J17" t="s">
         <v>484</v>
       </c>
       <c r="K17" t="s">
-        <v>383</v>
+        <v>516</v>
       </c>
       <c r="L17" t="s">
         <v>22</v>
@@ -21601,10 +21541,10 @@
         <v>378</v>
       </c>
       <c r="J18" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="K18" t="s">
-        <v>649</v>
+        <v>94</v>
       </c>
       <c r="L18" t="s">
         <v>22</v>
@@ -21633,13 +21573,13 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G19" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="H19" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="I19" t="s">
         <v>339</v>
@@ -21648,7 +21588,7 @@
         <v>216</v>
       </c>
       <c r="K19" t="s">
-        <v>320</v>
+        <v>249</v>
       </c>
       <c r="L19" t="s">
         <v>61</v>
@@ -21680,19 +21620,19 @@
         <v>289</v>
       </c>
       <c r="G20" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="H20" t="s">
         <v>101</v>
       </c>
       <c r="I20" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="J20" t="s">
         <v>162</v>
       </c>
       <c r="K20" t="s">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
@@ -21733,10 +21673,10 @@
         <v>40</v>
       </c>
       <c r="J21" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="K21" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="L21" t="s">
         <v>22</v>
@@ -21765,7 +21705,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="G22" t="s">
         <v>84</v>
@@ -21777,7 +21717,7 @@
         <v>116</v>
       </c>
       <c r="K22" t="s">
-        <v>672</v>
+        <v>98</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
@@ -21821,7 +21761,7 @@
         <v>255</v>
       </c>
       <c r="K23" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="L23" t="s">
         <v>22</v>
@@ -21850,22 +21790,22 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="G24" t="s">
         <v>207</v>
       </c>
       <c r="H24" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="I24" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="J24" t="s">
         <v>18</v>
       </c>
       <c r="K24" t="s">
-        <v>348</v>
+        <v>527</v>
       </c>
       <c r="L24" t="s">
         <v>22</v>
@@ -21894,7 +21834,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="G25" t="s">
         <v>130</v>
@@ -21903,13 +21843,13 @@
         <v>210</v>
       </c>
       <c r="I25" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="J25" t="s">
         <v>334</v>
       </c>
       <c r="K25" t="s">
-        <v>259</v>
+        <v>500</v>
       </c>
       <c r="L25" t="s">
         <v>22</v>
@@ -21944,16 +21884,16 @@
         <v>56</v>
       </c>
       <c r="H26" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="I26" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="J26" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="K26" t="s">
-        <v>145</v>
+        <v>401</v>
       </c>
       <c r="L26" t="s">
         <v>22</v>
@@ -21991,13 +21931,13 @@
         <v>476</v>
       </c>
       <c r="I27" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="J27" t="s">
         <v>63</v>
       </c>
       <c r="K27" t="s">
-        <v>630</v>
+        <v>92</v>
       </c>
       <c r="L27" t="s">
         <v>22</v>
@@ -22029,7 +21969,7 @@
         <v>458</v>
       </c>
       <c r="G28" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="H28" t="s">
         <v>377</v>
@@ -22041,7 +21981,7 @@
         <v>388</v>
       </c>
       <c r="K28" t="s">
-        <v>434</v>
+        <v>529</v>
       </c>
       <c r="L28" t="s">
         <v>61</v>
@@ -22085,7 +22025,7 @@
         <v>522</v>
       </c>
       <c r="K29" t="s">
-        <v>325</v>
+        <v>121</v>
       </c>
       <c r="L29" t="s">
         <v>22</v>
@@ -22114,7 +22054,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="G30" t="s">
         <v>314</v>
@@ -22129,7 +22069,7 @@
         <v>146</v>
       </c>
       <c r="K30" t="s">
-        <v>677</v>
+        <v>532</v>
       </c>
       <c r="L30" t="s">
         <v>22</v>
@@ -22158,7 +22098,7 @@
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="G31" t="s">
         <v>408</v>
@@ -22173,7 +22113,7 @@
         <v>484</v>
       </c>
       <c r="K31" t="s">
-        <v>64</v>
+        <v>366</v>
       </c>
       <c r="L31" t="s">
         <v>22</v>
@@ -22208,7 +22148,7 @@
         <v>107</v>
       </c>
       <c r="H32" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="I32" t="s">
         <v>275</v>
@@ -22217,7 +22157,7 @@
         <v>311</v>
       </c>
       <c r="K32" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -22246,10 +22186,10 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="G33" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="H33" t="s">
         <v>188</v>
@@ -22261,7 +22201,7 @@
         <v>83</v>
       </c>
       <c r="K33" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
@@ -22293,19 +22233,19 @@
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="H34" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="I34" t="s">
         <v>103</v>
       </c>
       <c r="J34" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
+        <v>469</v>
       </c>
       <c r="L34" t="s">
         <v>22</v>
@@ -22334,22 +22274,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G35" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="H35" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="I35" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="J35" t="s">
         <v>133</v>
       </c>
       <c r="K35" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L35" t="s">
         <v>22</v>
@@ -22387,13 +22327,13 @@
         <v>266</v>
       </c>
       <c r="I36" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J36" t="s">
         <v>487</v>
       </c>
       <c r="K36" t="s">
-        <v>524</v>
+        <v>483</v>
       </c>
       <c r="L36" t="s">
         <v>22</v>
@@ -22437,7 +22377,7 @@
         <v>248</v>
       </c>
       <c r="K37" t="s">
-        <v>405</v>
+        <v>363</v>
       </c>
       <c r="L37" t="s">
         <v>61</v>
@@ -22466,13 +22406,13 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G38" t="s">
         <v>441</v>
       </c>
       <c r="H38" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="I38" t="s">
         <v>407</v>
@@ -22481,7 +22421,7 @@
         <v>409</v>
       </c>
       <c r="K38" t="s">
-        <v>682</v>
+        <v>546</v>
       </c>
       <c r="L38" t="s">
         <v>22</v>
@@ -22510,10 +22450,10 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="G39" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="H39" t="s">
         <v>314</v>
@@ -22525,7 +22465,7 @@
         <v>40</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="L39" t="s">
         <v>22</v>
@@ -22557,7 +22497,7 @@
         <v>368</v>
       </c>
       <c r="G40" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H40" t="s">
         <v>340</v>
@@ -22569,7 +22509,7 @@
         <v>347</v>
       </c>
       <c r="K40" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="L40" t="s">
         <v>22</v>
@@ -22604,16 +22544,16 @@
         <v>257</v>
       </c>
       <c r="H41" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="I41" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="J41" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="K41" t="s">
-        <v>152</v>
+        <v>549</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
@@ -22645,19 +22585,19 @@
         <v>292</v>
       </c>
       <c r="G42" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="H42" t="s">
         <v>58</v>
       </c>
       <c r="I42" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J42" t="s">
         <v>367</v>
       </c>
       <c r="K42" t="s">
-        <v>289</v>
+        <v>551</v>
       </c>
       <c r="L42" t="s">
         <v>22</v>
@@ -22695,13 +22635,13 @@
         <v>535</v>
       </c>
       <c r="I43" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="J43" t="s">
         <v>196</v>
       </c>
       <c r="K43" t="s">
-        <v>30</v>
+        <v>358</v>
       </c>
       <c r="L43" t="s">
         <v>22</v>
@@ -22745,7 +22685,7 @@
         <v>468</v>
       </c>
       <c r="K44" t="s">
-        <v>49</v>
+        <v>556</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
@@ -22774,22 +22714,22 @@
         <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G45" t="s">
         <v>487</v>
       </c>
       <c r="H45" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="I45" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="J45" t="s">
         <v>301</v>
       </c>
       <c r="K45" t="s">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="L45" t="s">
         <v>22</v>
@@ -22833,7 +22773,7 @@
         <v>513</v>
       </c>
       <c r="K46" t="s">
-        <v>376</v>
+        <v>292</v>
       </c>
       <c r="L46" t="s">
         <v>22</v>
@@ -22862,7 +22802,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="G47" t="s">
         <v>312</v>
@@ -22877,7 +22817,7 @@
         <v>341</v>
       </c>
       <c r="K47" t="s">
-        <v>505</v>
+        <v>562</v>
       </c>
       <c r="L47" t="s">
         <v>22</v>
@@ -22906,22 +22846,22 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G48" t="s">
         <v>308</v>
       </c>
       <c r="H48" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="I48" t="s">
         <v>81</v>
       </c>
       <c r="J48" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="K48" t="s">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c r="L48" t="s">
         <v>22</v>
@@ -22965,7 +22905,7 @@
         <v>152</v>
       </c>
       <c r="K49" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="L49" t="s">
         <v>22</v>
@@ -22997,7 +22937,7 @@
         <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -23009,7 +22949,7 @@
         <v>33</v>
       </c>
       <c r="K50" t="s">
-        <v>165</v>
+        <v>568</v>
       </c>
       <c r="L50" t="s">
         <v>22</v>
@@ -23038,7 +22978,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="G51" t="s">
         <v>461</v>
@@ -23047,13 +22987,13 @@
         <v>330</v>
       </c>
       <c r="I51" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="J51" t="s">
         <v>40</v>
       </c>
       <c r="K51" t="s">
-        <v>343</v>
+        <v>69</v>
       </c>
       <c r="L51" t="s">
         <v>22</v>
@@ -23085,7 +23025,7 @@
         <v>179</v>
       </c>
       <c r="G52" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="H52" t="s">
         <v>128</v>
@@ -23094,10 +23034,10 @@
         <v>441</v>
       </c>
       <c r="J52" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="K52" t="s">
-        <v>689</v>
+        <v>450</v>
       </c>
       <c r="L52" t="s">
         <v>61</v>
@@ -23126,22 +23066,22 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="G53" t="s">
         <v>258</v>
       </c>
       <c r="H53" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="I53" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="J53" t="s">
         <v>292</v>
       </c>
       <c r="K53" t="s">
-        <v>492</v>
+        <v>572</v>
       </c>
       <c r="L53" t="s">
         <v>22</v>
@@ -23173,7 +23113,7 @@
         <v>174</v>
       </c>
       <c r="G54" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="H54" t="s">
         <v>518</v>
@@ -23185,7 +23125,7 @@
         <v>208</v>
       </c>
       <c r="K54" t="s">
-        <v>691</v>
+        <v>282</v>
       </c>
       <c r="L54" t="s">
         <v>22</v>
@@ -23217,7 +23157,7 @@
         <v>532</v>
       </c>
       <c r="G55" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="H55" t="s">
         <v>213</v>
@@ -23229,7 +23169,7 @@
         <v>329</v>
       </c>
       <c r="K55" t="s">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="L55" t="s">
         <v>22</v>
@@ -23267,13 +23207,13 @@
         <v>27</v>
       </c>
       <c r="I56" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="J56" t="s">
         <v>306</v>
       </c>
       <c r="K56" t="s">
-        <v>357</v>
+        <v>422</v>
       </c>
       <c r="L56" t="s">
         <v>22</v>
@@ -23302,7 +23242,7 @@
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G57" t="s">
         <v>361</v>
@@ -23311,13 +23251,13 @@
         <v>48</v>
       </c>
       <c r="I57" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="J57" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="K57" t="s">
-        <v>663</v>
+        <v>30</v>
       </c>
       <c r="L57" t="s">
         <v>22</v>
@@ -23361,7 +23301,7 @@
         <v>153</v>
       </c>
       <c r="K58" t="s">
-        <v>516</v>
+        <v>217</v>
       </c>
       <c r="L58" t="s">
         <v>22</v>
@@ -23390,22 +23330,22 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="G59" t="s">
         <v>491</v>
       </c>
       <c r="H59" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="I59" t="s">
         <v>297</v>
       </c>
       <c r="J59" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="K59" t="s">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="L59" t="s">
         <v>22</v>
@@ -23434,22 +23374,22 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="G60" t="s">
         <v>451</v>
       </c>
       <c r="H60" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="I60" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="J60" t="s">
         <v>107</v>
       </c>
       <c r="K60" t="s">
-        <v>141</v>
+        <v>562</v>
       </c>
       <c r="L60" t="s">
         <v>61</v>
@@ -23493,7 +23433,7 @@
         <v>40</v>
       </c>
       <c r="K61" t="s">
-        <v>73</v>
+        <v>580</v>
       </c>
       <c r="L61" t="s">
         <v>22</v>
@@ -23528,7 +23468,7 @@
         <v>113</v>
       </c>
       <c r="H62" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="I62" t="s">
         <v>291</v>
@@ -23537,7 +23477,7 @@
         <v>215</v>
       </c>
       <c r="K62" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="L62" t="s">
         <v>22</v>
@@ -23572,7 +23512,7 @@
         <v>33</v>
       </c>
       <c r="H63" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="I63" t="s">
         <v>41</v>
@@ -23581,7 +23521,7 @@
         <v>505</v>
       </c>
       <c r="K63" t="s">
-        <v>637</v>
+        <v>437</v>
       </c>
       <c r="L63" t="s">
         <v>22</v>
@@ -23610,10 +23550,10 @@
         <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G64" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="H64" t="s">
         <v>201</v>
@@ -23625,7 +23565,7 @@
         <v>539</v>
       </c>
       <c r="K64" t="s">
-        <v>697</v>
+        <v>584</v>
       </c>
       <c r="L64" t="s">
         <v>22</v>
@@ -23669,7 +23609,7 @@
         <v>30</v>
       </c>
       <c r="K65" t="s">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="L65" t="s">
         <v>22</v>
@@ -23698,13 +23638,13 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G66" t="s">
         <v>138</v>
       </c>
       <c r="H66" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="I66" t="s">
         <v>103</v>
@@ -23713,7 +23653,7 @@
         <v>185</v>
       </c>
       <c r="K66" t="s">
-        <v>698</v>
+        <v>415</v>
       </c>
       <c r="L66" t="s">
         <v>22</v>
@@ -23745,7 +23685,7 @@
         <v>109</v>
       </c>
       <c r="G67" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H67" t="s">
         <v>281</v>
@@ -23757,7 +23697,7 @@
         <v>374</v>
       </c>
       <c r="K67" t="s">
-        <v>669</v>
+        <v>187</v>
       </c>
       <c r="L67" t="s">
         <v>61</v>
@@ -23792,7 +23732,7 @@
         <v>537</v>
       </c>
       <c r="H68" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="I68" t="s">
         <v>468</v>
@@ -23801,7 +23741,7 @@
         <v>284</v>
       </c>
       <c r="K68" t="s">
-        <v>183</v>
+        <v>561</v>
       </c>
       <c r="L68" t="s">
         <v>22</v>
@@ -23845,7 +23785,7 @@
         <v>422</v>
       </c>
       <c r="K69" t="s">
-        <v>478</v>
+        <v>591</v>
       </c>
       <c r="L69" t="s">
         <v>22</v>
@@ -23877,7 +23817,7 @@
         <v>200</v>
       </c>
       <c r="G70" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="H70" t="s">
         <v>366</v>
@@ -23889,7 +23829,7 @@
         <v>35</v>
       </c>
       <c r="K70" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="L70" t="s">
         <v>22</v>
@@ -23921,19 +23861,19 @@
         <v>48</v>
       </c>
       <c r="G71" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="H71" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I71" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="J71" t="s">
         <v>269</v>
       </c>
       <c r="K71" t="s">
-        <v>442</v>
+        <v>372</v>
       </c>
       <c r="L71" t="s">
         <v>22</v>
@@ -23977,7 +23917,7 @@
         <v>478</v>
       </c>
       <c r="K72" t="s">
-        <v>702</v>
+        <v>211</v>
       </c>
       <c r="L72" t="s">
         <v>22</v>
@@ -24006,7 +23946,7 @@
         <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="G73" t="s">
         <v>206</v>
@@ -24021,7 +23961,7 @@
         <v>431</v>
       </c>
       <c r="K73" t="s">
-        <v>60</v>
+        <v>598</v>
       </c>
       <c r="L73" t="s">
         <v>22</v>
@@ -24050,7 +23990,7 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G74" t="s">
         <v>525</v>
@@ -24065,7 +24005,7 @@
         <v>170</v>
       </c>
       <c r="K74" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="L74" t="s">
         <v>22</v>
@@ -24094,7 +24034,7 @@
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="G75" t="s">
         <v>200</v>
@@ -24109,7 +24049,7 @@
         <v>516</v>
       </c>
       <c r="K75" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="L75" t="s">
         <v>22</v>
@@ -24138,7 +24078,7 @@
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="G76" t="s">
         <v>337</v>
@@ -24147,13 +24087,13 @@
         <v>137</v>
       </c>
       <c r="I76" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="J76" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="K76" t="s">
-        <v>556</v>
+        <v>208</v>
       </c>
       <c r="L76" t="s">
         <v>22</v>
@@ -24185,19 +24125,19 @@
         <v>188</v>
       </c>
       <c r="G77" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="H77" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="I77" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="J77" t="s">
         <v>280</v>
       </c>
       <c r="K77" t="s">
-        <v>325</v>
+        <v>54</v>
       </c>
       <c r="L77" t="s">
         <v>22</v>
@@ -24241,7 +24181,7 @@
         <v>193</v>
       </c>
       <c r="K78" t="s">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="L78" t="s">
         <v>22</v>
@@ -24279,13 +24219,13 @@
         <v>137</v>
       </c>
       <c r="I79" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="J79" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="K79" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="L79" t="s">
         <v>22</v>
@@ -24314,19 +24254,19 @@
         <v>2</v>
       </c>
       <c r="F80" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="G80" t="s">
         <v>536</v>
       </c>
       <c r="H80" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="I80" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="J80" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="K80" t="s">
         <v>508</v>
@@ -24366,14 +24306,14 @@
       <c r="H81" t="s">
         <v>454</v>
       </c>
-      <c r="I81" t="s">
-        <v>668</v>
+      <c r="I81">
+        <v>100</v>
       </c>
       <c r="J81" t="s">
         <v>334</v>
       </c>
       <c r="K81" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="L81" t="s">
         <v>22</v>
@@ -24410,8 +24350,8 @@
       <c r="H82" t="s">
         <v>336</v>
       </c>
-      <c r="I82" t="s">
-        <v>409</v>
+      <c r="I82">
+        <v>100</v>
       </c>
       <c r="J82" t="s">
         <v>145</v>
@@ -24446,7 +24386,7 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G83" t="s">
         <v>397</v>
@@ -24454,11 +24394,11 @@
       <c r="H83" t="s">
         <v>157</v>
       </c>
-      <c r="I83" t="s">
-        <v>369</v>
+      <c r="I83">
+        <v>100</v>
       </c>
       <c r="J83" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="K83" t="s">
         <v>77</v>
@@ -24490,16 +24430,16 @@
         <v>2</v>
       </c>
       <c r="F84" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="G84" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="H84" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="I84" t="s">
-        <v>264</v>
+        <v>38</v>
       </c>
       <c r="J84" t="s">
         <v>292</v>
@@ -24534,22 +24474,22 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="G85" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="H85" t="s">
         <v>488</v>
       </c>
       <c r="I85" t="s">
-        <v>463</v>
+        <v>83</v>
       </c>
       <c r="J85" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="K85" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="L85" t="s">
         <v>22</v>
@@ -24581,13 +24521,13 @@
         <v>485</v>
       </c>
       <c r="G86" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="H86" t="s">
         <v>179</v>
       </c>
       <c r="I86" t="s">
-        <v>709</v>
+        <v>86</v>
       </c>
       <c r="J86" t="s">
         <v>99</v>
@@ -24631,7 +24571,7 @@
         <v>273</v>
       </c>
       <c r="I87" t="s">
-        <v>591</v>
+        <v>17</v>
       </c>
       <c r="J87" t="s">
         <v>385</v>
@@ -24675,13 +24615,13 @@
         <v>322</v>
       </c>
       <c r="I88" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="J88" t="s">
         <v>407</v>
       </c>
       <c r="K88" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="L88" t="s">
         <v>22</v>
@@ -24719,7 +24659,7 @@
         <v>440</v>
       </c>
       <c r="I89" t="s">
-        <v>312</v>
+        <v>16</v>
       </c>
       <c r="J89" t="s">
         <v>193</v>
@@ -24760,10 +24700,10 @@
         <v>84</v>
       </c>
       <c r="H90" t="s">
-        <v>593</v>
-      </c>
-      <c r="I90" t="s">
-        <v>602</v>
+        <v>590</v>
+      </c>
+      <c r="I90">
+        <v>100</v>
       </c>
       <c r="J90" t="s">
         <v>93</v>
@@ -24804,13 +24744,13 @@
         <v>217</v>
       </c>
       <c r="H91" t="s">
-        <v>705</v>
-      </c>
-      <c r="I91" t="s">
-        <v>332</v>
+        <v>687</v>
+      </c>
+      <c r="I91">
+        <v>100</v>
       </c>
       <c r="J91" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="K91" t="s">
         <v>192</v>
@@ -24848,10 +24788,10 @@
         <v>217</v>
       </c>
       <c r="H92" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="I92" t="s">
-        <v>597</v>
+        <v>33</v>
       </c>
       <c r="J92" t="s">
         <v>127</v>
@@ -24892,10 +24832,10 @@
         <v>333</v>
       </c>
       <c r="H93" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I93" t="s">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="J93" t="s">
         <v>172</v>
@@ -24930,22 +24870,22 @@
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="G94" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="H94" t="s">
         <v>288</v>
       </c>
       <c r="I94" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="J94" t="s">
         <v>156</v>
       </c>
       <c r="K94" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="L94" t="s">
         <v>22</v>
@@ -24977,13 +24917,13 @@
         <v>429</v>
       </c>
       <c r="G95" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H95" t="s">
         <v>532</v>
       </c>
       <c r="I95" t="s">
-        <v>464</v>
+        <v>69</v>
       </c>
       <c r="J95" t="s">
         <v>250</v>
@@ -25024,10 +24964,10 @@
         <v>410</v>
       </c>
       <c r="H96" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="I96" t="s">
-        <v>463</v>
+        <v>44</v>
       </c>
       <c r="J96" t="s">
         <v>144</v>
@@ -25071,7 +25011,7 @@
         <v>159</v>
       </c>
       <c r="I97" t="s">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="J97" t="s">
         <v>357</v>
@@ -25109,16 +25049,16 @@
         <v>492</v>
       </c>
       <c r="G98" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="H98" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="I98" t="s">
-        <v>468</v>
+        <v>72</v>
       </c>
       <c r="J98" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="K98" t="s">
         <v>173</v>
@@ -25159,10 +25099,10 @@
         <v>408</v>
       </c>
       <c r="I99" t="s">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c r="J99" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="K99" t="s">
         <v>153</v>
@@ -25203,13 +25143,13 @@
         <v>120</v>
       </c>
       <c r="I100" t="s">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="J100" t="s">
         <v>462</v>
       </c>
       <c r="K100" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="L100" t="s">
         <v>22</v>
@@ -25246,8 +25186,8 @@
       <c r="H101" t="s">
         <v>200</v>
       </c>
-      <c r="I101" t="s">
-        <v>165</v>
+      <c r="I101">
+        <v>100</v>
       </c>
       <c r="J101" t="s">
         <v>215</v>
@@ -25282,7 +25222,7 @@
         <v>2</v>
       </c>
       <c r="F102" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="G102" t="s">
         <v>149</v>
@@ -25291,7 +25231,7 @@
         <v>528</v>
       </c>
       <c r="I102" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J102" t="s">
         <v>155</v>
@@ -25335,7 +25275,7 @@
         <v>256</v>
       </c>
       <c r="I103" t="s">
-        <v>607</v>
+        <v>68</v>
       </c>
       <c r="J103" t="s">
         <v>218</v>
@@ -25379,7 +25319,7 @@
         <v>300</v>
       </c>
       <c r="I104" t="s">
-        <v>273</v>
+        <v>25</v>
       </c>
       <c r="J104" t="s">
         <v>295</v>
@@ -25423,10 +25363,10 @@
         <v>95</v>
       </c>
       <c r="I105" t="s">
-        <v>299</v>
+        <v>35</v>
       </c>
       <c r="J105" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="K105" t="s">
         <v>460</v>
@@ -25464,16 +25404,16 @@
         <v>468</v>
       </c>
       <c r="H106" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I106" t="s">
-        <v>316</v>
+        <v>69</v>
       </c>
       <c r="J106" t="s">
         <v>161</v>
       </c>
       <c r="K106" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L106" t="s">
         <v>22</v>
@@ -25508,13 +25448,13 @@
         <v>87</v>
       </c>
       <c r="H107" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I107" t="s">
-        <v>711</v>
+        <v>47</v>
       </c>
       <c r="J107" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="K107" t="s">
         <v>189</v>
@@ -25555,13 +25495,13 @@
         <v>75</v>
       </c>
       <c r="I108" t="s">
-        <v>365</v>
+        <v>16</v>
       </c>
       <c r="J108" t="s">
         <v>18</v>
       </c>
       <c r="K108" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="L108" t="s">
         <v>22</v>
@@ -25599,7 +25539,7 @@
         <v>391</v>
       </c>
       <c r="I109" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="J109" t="s">
         <v>134</v>
@@ -25643,7 +25583,7 @@
         <v>271</v>
       </c>
       <c r="I110" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J110" t="s">
         <v>17</v>
@@ -25678,7 +25618,7 @@
         <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="G111" t="s">
         <v>421</v>
@@ -25687,13 +25627,13 @@
         <v>131</v>
       </c>
       <c r="I111" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="J111" t="s">
         <v>539</v>
       </c>
       <c r="K111" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L111" t="s">
         <v>22</v>
@@ -25722,7 +25662,7 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="G112" t="s">
         <v>424</v>
@@ -25731,7 +25671,7 @@
         <v>478</v>
       </c>
       <c r="I112" t="s">
-        <v>713</v>
+        <v>83</v>
       </c>
       <c r="J112" t="s">
         <v>360</v>
@@ -25769,19 +25709,19 @@
         <v>397</v>
       </c>
       <c r="G113" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="H113" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="I113" t="s">
-        <v>591</v>
+        <v>42</v>
       </c>
       <c r="J113" t="s">
         <v>210</v>
       </c>
       <c r="K113" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="L113" t="s">
         <v>22</v>
@@ -25816,10 +25756,10 @@
         <v>49</v>
       </c>
       <c r="H114" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="I114" t="s">
-        <v>357</v>
+        <v>16</v>
       </c>
       <c r="J114" t="s">
         <v>538</v>
@@ -25863,7 +25803,7 @@
         <v>163</v>
       </c>
       <c r="I115" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="J115" t="s">
         <v>215</v>
@@ -25904,10 +25844,10 @@
         <v>79</v>
       </c>
       <c r="H116" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="I116" t="s">
-        <v>631</v>
+        <v>30</v>
       </c>
       <c r="J116" t="s">
         <v>111</v>
@@ -25951,13 +25891,13 @@
         <v>220</v>
       </c>
       <c r="I117" t="s">
-        <v>267</v>
+        <v>83</v>
       </c>
       <c r="J117" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K117" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="L117" t="s">
         <v>22</v>
@@ -25992,13 +25932,13 @@
         <v>455</v>
       </c>
       <c r="H118" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I118" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="J118" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="K118" t="s">
         <v>427</v>
@@ -26039,7 +25979,7 @@
         <v>69</v>
       </c>
       <c r="I119" t="s">
-        <v>334</v>
+        <v>35</v>
       </c>
       <c r="J119" t="s">
         <v>346</v>
@@ -26077,13 +26017,13 @@
         <v>533</v>
       </c>
       <c r="G120" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="H120" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="I120" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="J120" t="s">
         <v>431</v>
@@ -26127,7 +26067,7 @@
         <v>464</v>
       </c>
       <c r="I121" t="s">
-        <v>260</v>
+        <v>86</v>
       </c>
       <c r="J121" t="s">
         <v>92</v>
@@ -26168,10 +26108,10 @@
         <v>221</v>
       </c>
       <c r="H122" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I122" t="s">
-        <v>700</v>
+        <v>87</v>
       </c>
       <c r="J122" t="s">
         <v>147</v>
@@ -26209,19 +26149,19 @@
         <v>416</v>
       </c>
       <c r="G123" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="H123" t="s">
         <v>299</v>
       </c>
       <c r="I123" t="s">
-        <v>570</v>
+        <v>30</v>
       </c>
       <c r="J123" t="s">
         <v>58</v>
       </c>
       <c r="K123" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L123" t="s">
         <v>22</v>
@@ -26250,22 +26190,22 @@
         <v>2</v>
       </c>
       <c r="F124" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="G124" t="s">
         <v>387</v>
       </c>
       <c r="H124" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="I124" t="s">
-        <v>474</v>
+        <v>19</v>
       </c>
       <c r="J124" t="s">
         <v>25</v>
       </c>
       <c r="K124" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="L124" t="s">
         <v>22</v>
@@ -26303,7 +26243,7 @@
         <v>195</v>
       </c>
       <c r="I125" t="s">
-        <v>715</v>
+        <v>30</v>
       </c>
       <c r="J125" t="s">
         <v>213</v>
@@ -26347,10 +26287,10 @@
         <v>107</v>
       </c>
       <c r="I126" t="s">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="J126" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="K126" t="s">
         <v>98</v>
@@ -26382,22 +26322,22 @@
         <v>1</v>
       </c>
       <c r="F127" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
       <c r="G127" t="s">
-        <v>717</v>
+        <v>698</v>
       </c>
       <c r="H127" t="s">
         <v>251</v>
       </c>
       <c r="I127" t="s">
-        <v>553</v>
+        <v>38</v>
       </c>
       <c r="J127" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="K127" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L127" t="s">
         <v>61</v>
@@ -26435,7 +26375,7 @@
         <v>313</v>
       </c>
       <c r="I128" t="s">
-        <v>372</v>
+        <v>102</v>
       </c>
       <c r="J128" t="s">
         <v>512</v>
@@ -26470,7 +26410,7 @@
         <v>2</v>
       </c>
       <c r="F129" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="G129" t="s">
         <v>508</v>
@@ -26479,13 +26419,13 @@
         <v>154</v>
       </c>
       <c r="I129" t="s">
-        <v>481</v>
+        <v>47</v>
       </c>
       <c r="J129" t="s">
         <v>255</v>
       </c>
       <c r="K129" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="L129" t="s">
         <v>22</v>
@@ -26523,7 +26463,7 @@
         <v>520</v>
       </c>
       <c r="I130" t="s">
-        <v>531</v>
+        <v>35</v>
       </c>
       <c r="J130" t="s">
         <v>382</v>
@@ -26567,13 +26507,13 @@
         <v>44</v>
       </c>
       <c r="I131" t="s">
-        <v>283</v>
+        <v>158</v>
       </c>
       <c r="J131" t="s">
         <v>264</v>
       </c>
       <c r="K131" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L131" t="s">
         <v>22</v>
@@ -26611,7 +26551,7 @@
         <v>467</v>
       </c>
       <c r="I132" t="s">
-        <v>623</v>
+        <v>66</v>
       </c>
       <c r="J132" t="s">
         <v>48</v>
@@ -26655,7 +26595,7 @@
         <v>305</v>
       </c>
       <c r="I133" t="s">
-        <v>211</v>
+        <v>25</v>
       </c>
       <c r="J133" t="s">
         <v>177</v>
@@ -26690,22 +26630,22 @@
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="G134" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="H134" t="s">
         <v>135</v>
       </c>
       <c r="I134" t="s">
-        <v>704</v>
+        <v>83</v>
       </c>
       <c r="J134" t="s">
         <v>217</v>
       </c>
       <c r="K134" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="L134" t="s">
         <v>22</v>
@@ -26743,10 +26683,10 @@
         <v>524</v>
       </c>
       <c r="I135" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="J135" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="K135" t="s">
         <v>52</v>
@@ -26778,7 +26718,7 @@
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G136" t="s">
         <v>200</v>
@@ -26787,7 +26727,7 @@
         <v>141</v>
       </c>
       <c r="I136" t="s">
-        <v>557</v>
+        <v>52</v>
       </c>
       <c r="J136" t="s">
         <v>215</v>
@@ -26825,13 +26765,13 @@
         <v>434</v>
       </c>
       <c r="G137" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="H137" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="I137" t="s">
-        <v>216</v>
+        <v>64</v>
       </c>
       <c r="J137" t="s">
         <v>341</v>
@@ -26869,13 +26809,13 @@
         <v>20</v>
       </c>
       <c r="G138" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H138" t="s">
         <v>75</v>
       </c>
       <c r="I138" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="J138" t="s">
         <v>32</v>
@@ -26910,22 +26850,22 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="G139" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="H139" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="I139" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="J139" t="s">
         <v>462</v>
       </c>
       <c r="K139" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="L139" t="s">
         <v>22</v>
@@ -26963,13 +26903,13 @@
         <v>398</v>
       </c>
       <c r="I140" t="s">
-        <v>653</v>
+        <v>27</v>
       </c>
       <c r="J140" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K140" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="L140" t="s">
         <v>22</v>
@@ -27007,10 +26947,10 @@
         <v>537</v>
       </c>
       <c r="I141" t="s">
-        <v>630</v>
+        <v>64</v>
       </c>
       <c r="J141" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="K141" t="s">
         <v>118</v>
@@ -27045,19 +26985,19 @@
         <v>496</v>
       </c>
       <c r="G142" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="H142" t="s">
         <v>142</v>
       </c>
       <c r="I142" t="s">
-        <v>434</v>
+        <v>68</v>
       </c>
       <c r="J142" t="s">
         <v>173</v>
       </c>
       <c r="K142" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L142" t="s">
         <v>61</v>
@@ -27095,7 +27035,7 @@
         <v>131</v>
       </c>
       <c r="I143" t="s">
-        <v>702</v>
+        <v>21</v>
       </c>
       <c r="J143" t="s">
         <v>116</v>
@@ -27139,13 +27079,13 @@
         <v>74</v>
       </c>
       <c r="I144" t="s">
-        <v>720</v>
+        <v>87</v>
       </c>
       <c r="J144" t="s">
         <v>215</v>
       </c>
       <c r="K144" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="L144" t="s">
         <v>22</v>
@@ -27183,7 +27123,7 @@
         <v>501</v>
       </c>
       <c r="I145" t="s">
-        <v>369</v>
+        <v>68</v>
       </c>
       <c r="J145" t="s">
         <v>174</v>
@@ -27227,10 +27167,10 @@
         <v>525</v>
       </c>
       <c r="I146" t="s">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="K146" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L146" t="s">
         <v>22</v>
@@ -27259,19 +27199,19 @@
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="G147" t="s">
         <v>357</v>
       </c>
       <c r="H147" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="I147" t="s">
-        <v>320</v>
+        <v>48</v>
       </c>
       <c r="J147" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="K147" t="s">
         <v>152</v>
@@ -27303,7 +27243,7 @@
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="G148" t="s">
         <v>420</v>
@@ -27311,11 +27251,11 @@
       <c r="H148" t="s">
         <v>360</v>
       </c>
-      <c r="I148" t="s">
-        <v>519</v>
+      <c r="I148">
+        <v>100</v>
       </c>
       <c r="J148" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="K148" t="s">
         <v>371</v>
@@ -27355,8 +27295,8 @@
       <c r="H149" t="s">
         <v>433</v>
       </c>
-      <c r="I149" t="s">
-        <v>504</v>
+      <c r="I149">
+        <v>100</v>
       </c>
       <c r="J149" t="s">
         <v>338</v>
@@ -27391,16 +27331,16 @@
         <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G150" t="s">
         <v>148</v>
       </c>
       <c r="H150" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="I150" t="s">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="J150" t="s">
         <v>174</v>
@@ -27435,7 +27375,7 @@
         <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G151" t="s">
         <v>193</v>
@@ -27444,7 +27384,7 @@
         <v>139</v>
       </c>
       <c r="I151" t="s">
-        <v>596</v>
+        <v>26</v>
       </c>
       <c r="J151" t="s">
         <v>26</v>
@@ -27479,7 +27419,7 @@
         <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="G152" t="s">
         <v>403</v>
@@ -27488,7 +27428,7 @@
         <v>98</v>
       </c>
       <c r="I152" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="J152" t="s">
         <v>76</v>
@@ -27523,7 +27463,7 @@
         <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="G153" t="s">
         <v>86</v>
@@ -27532,7 +27472,7 @@
         <v>452</v>
       </c>
       <c r="I153" t="s">
-        <v>501</v>
+        <v>99</v>
       </c>
       <c r="J153" t="s">
         <v>448</v>
@@ -27576,7 +27516,7 @@
         <v>345</v>
       </c>
       <c r="I154" t="s">
-        <v>386</v>
+        <v>92</v>
       </c>
       <c r="J154" t="s">
         <v>124</v>
@@ -27614,13 +27554,13 @@
         <v>33</v>
       </c>
       <c r="G155" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="H155" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="I155" t="s">
-        <v>568</v>
+        <v>47</v>
       </c>
       <c r="J155" t="s">
         <v>487</v>
@@ -27655,7 +27595,7 @@
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="G156" t="s">
         <v>58</v>
@@ -27664,7 +27604,7 @@
         <v>266</v>
       </c>
       <c r="I156" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="J156" t="s">
         <v>205</v>
@@ -27707,8 +27647,8 @@
       <c r="H157" t="s">
         <v>430</v>
       </c>
-      <c r="I157" t="s">
-        <v>64</v>
+      <c r="I157">
+        <v>100</v>
       </c>
       <c r="J157" t="s">
         <v>60</v>
@@ -27743,22 +27683,22 @@
         <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G158" t="s">
         <v>194</v>
       </c>
       <c r="H158" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="I158" t="s">
-        <v>498</v>
+        <v>44</v>
       </c>
       <c r="J158" t="s">
         <v>73</v>
       </c>
       <c r="K158" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="L158" t="s">
         <v>22</v>
@@ -27796,13 +27736,13 @@
         <v>160</v>
       </c>
       <c r="I159" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="J159" t="s">
         <v>359</v>
       </c>
       <c r="K159" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="L159" t="s">
         <v>22</v>
@@ -27831,16 +27771,16 @@
         <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="G160" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="H160" t="s">
         <v>347</v>
       </c>
       <c r="I160" t="s">
-        <v>471</v>
+        <v>44</v>
       </c>
       <c r="J160" t="s">
         <v>213</v>
@@ -27884,7 +27824,7 @@
         <v>475</v>
       </c>
       <c r="I161" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="J161" t="s">
         <v>120</v>
@@ -27922,13 +27862,13 @@
         <v>157</v>
       </c>
       <c r="G162" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H162" t="s">
         <v>99</v>
       </c>
       <c r="I162" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J162" t="s">
         <v>175</v>
@@ -27969,16 +27909,16 @@
         <v>472</v>
       </c>
       <c r="H163" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c r="I163" t="s">
-        <v>207</v>
+        <v>96</v>
       </c>
       <c r="J163" t="s">
         <v>493</v>
       </c>
       <c r="K163" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="L163" t="s">
         <v>22</v>
@@ -28013,16 +27953,16 @@
         <v>249</v>
       </c>
       <c r="H164" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I164" t="s">
-        <v>527</v>
+        <v>38</v>
       </c>
       <c r="J164" t="s">
         <v>334</v>
       </c>
       <c r="K164" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="L164" t="s">
         <v>22</v>
@@ -28051,22 +27991,22 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="G165" t="s">
         <v>335</v>
       </c>
       <c r="H165" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="I165" t="s">
-        <v>473</v>
+        <v>98</v>
       </c>
       <c r="J165" t="s">
         <v>68</v>
       </c>
       <c r="K165" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="L165" t="s">
         <v>61</v>
@@ -28098,13 +28038,13 @@
         <v>155</v>
       </c>
       <c r="G166" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="H166" t="s">
         <v>215</v>
       </c>
       <c r="I166" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="J166" t="s">
         <v>477</v>
@@ -28148,7 +28088,7 @@
         <v>266</v>
       </c>
       <c r="I167" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="J167" t="s">
         <v>330</v>
@@ -28186,13 +28126,13 @@
         <v>452</v>
       </c>
       <c r="G168" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H168" t="s">
         <v>143</v>
       </c>
       <c r="I168" t="s">
-        <v>724</v>
+        <v>81</v>
       </c>
       <c r="J168" t="s">
         <v>212</v>
@@ -28236,13 +28176,13 @@
         <v>272</v>
       </c>
       <c r="I169" t="s">
-        <v>434</v>
+        <v>25</v>
       </c>
       <c r="J169" t="s">
         <v>66</v>
       </c>
       <c r="K169" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="L169" t="s">
         <v>22</v>
@@ -28286,7 +28226,7 @@
         <v>137</v>
       </c>
       <c r="K170" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L170" t="s">
         <v>22</v>
@@ -28318,7 +28258,7 @@
         <v>50</v>
       </c>
       <c r="G171" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H171" t="s">
         <v>289</v>
@@ -28362,7 +28302,7 @@
         <v>302</v>
       </c>
       <c r="G172" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="H172" t="s">
         <v>456</v>
@@ -28403,16 +28343,16 @@
         <v>2</v>
       </c>
       <c r="F173" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="G173" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="H173" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="I173" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="J173" t="s">
         <v>460</v>
@@ -28450,13 +28390,13 @@
         <v>252</v>
       </c>
       <c r="G174" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="H174" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="I174" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J174" t="s">
         <v>435</v>
@@ -28538,13 +28478,13 @@
         <v>144</v>
       </c>
       <c r="G176" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="H176" t="s">
         <v>82</v>
       </c>
       <c r="I176" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J176" t="s">
         <v>301</v>
@@ -28629,16 +28569,16 @@
         <v>499</v>
       </c>
       <c r="H178" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I178" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="J178" t="s">
         <v>460</v>
       </c>
       <c r="K178" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="L178" t="s">
         <v>22</v>
@@ -28670,10 +28610,10 @@
         <v>424</v>
       </c>
       <c r="G179" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="H179" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="I179" t="s">
         <v>429</v>
@@ -28682,7 +28622,7 @@
         <v>51</v>
       </c>
       <c r="K179" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="L179" t="s">
         <v>22</v>
@@ -28711,7 +28651,7 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="G180" t="s">
         <v>364</v>
@@ -28720,10 +28660,10 @@
         <v>49</v>
       </c>
       <c r="I180" t="s">
-        <v>727</v>
+        <v>707</v>
       </c>
       <c r="J180" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="K180" t="s">
         <v>414</v>
@@ -28767,7 +28707,7 @@
         <v>492</v>
       </c>
       <c r="K181" t="s">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="L181" t="s">
         <v>22</v>
@@ -28805,7 +28745,7 @@
         <v>19</v>
       </c>
       <c r="I182" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="J182" t="s">
         <v>33</v>
@@ -28846,7 +28786,7 @@
         <v>114</v>
       </c>
       <c r="H183" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="I183" t="s">
         <v>458</v>
@@ -28855,7 +28795,7 @@
         <v>86</v>
       </c>
       <c r="K183" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="L183" t="s">
         <v>61</v>
@@ -28931,7 +28871,7 @@
         <v>417</v>
       </c>
       <c r="G185" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="H185" t="s">
         <v>359</v>
@@ -28978,7 +28918,7 @@
         <v>148</v>
       </c>
       <c r="H186" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="I186" t="s">
         <v>353</v>
@@ -29028,7 +28968,7 @@
         <v>19</v>
       </c>
       <c r="J187" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="K187" t="s">
         <v>301</v>
@@ -29066,7 +29006,7 @@
         <v>461</v>
       </c>
       <c r="H188" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="I188" t="s">
         <v>106</v>
@@ -29107,7 +29047,7 @@
         <v>267</v>
       </c>
       <c r="G189" t="s">
-        <v>729</v>
+        <v>709</v>
       </c>
       <c r="H189" t="s">
         <v>37</v>
@@ -29116,10 +29056,10 @@
         <v>176</v>
       </c>
       <c r="J189" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="K189" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L189" t="s">
         <v>22</v>
@@ -29148,7 +29088,7 @@
         <v>2</v>
       </c>
       <c r="F190" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G190" t="s">
         <v>541</v>
@@ -29157,13 +29097,13 @@
         <v>308</v>
       </c>
       <c r="I190" t="s">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="J190" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="K190" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L190" t="s">
         <v>22</v>
@@ -29192,13 +29132,13 @@
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>731</v>
+        <v>711</v>
       </c>
       <c r="G191" t="s">
         <v>528</v>
       </c>
       <c r="H191" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="I191" t="s">
         <v>278</v>
@@ -29236,13 +29176,13 @@
         <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G192" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="H192" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="I192" t="s">
         <v>431</v>
@@ -29280,10 +29220,10 @@
         <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="G193" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="H193" t="s">
         <v>516</v>
@@ -29292,7 +29232,7 @@
         <v>513</v>
       </c>
       <c r="J193" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="K193" t="s">
         <v>77</v>
@@ -29412,7 +29352,7 @@
         <v>1</v>
       </c>
       <c r="F196" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="G196" t="s">
         <v>263</v>
@@ -29456,7 +29396,7 @@
         <v>1</v>
       </c>
       <c r="F197" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="G197" t="s">
         <v>391</v>
@@ -29465,7 +29405,7 @@
         <v>250</v>
       </c>
       <c r="I197" t="s">
-        <v>732</v>
+        <v>712</v>
       </c>
       <c r="J197" t="s">
         <v>442</v>
@@ -29550,7 +29490,7 @@
         <v>488</v>
       </c>
       <c r="H199" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I199" t="s">
         <v>36</v>
@@ -29591,16 +29531,16 @@
         <v>378</v>
       </c>
       <c r="G200" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H200" t="s">
         <v>150</v>
       </c>
       <c r="I200" t="s">
-        <v>733</v>
+        <v>713</v>
       </c>
       <c r="J200" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="K200" t="s">
         <v>99</v>
@@ -29641,7 +29581,7 @@
         <v>534</v>
       </c>
       <c r="I201" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J201" t="s">
         <v>74</v>
